--- a/docs/firefly_card_benchmark_template.xlsx
+++ b/docs/firefly_card_benchmark_template.xlsx
@@ -1767,7 +1767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.38" customWidth="1" style="8" min="1" max="1"/>
@@ -1778,223 +1778,204 @@
     <row r="1" ht="15" customHeight="1" s="9">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>维度</t>
-        </is>
-      </c>
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>Firefly当前</t>
-        </is>
-      </c>
-      <c r="C1" s="11" t="inlineStr">
-        <is>
-          <t>Ironclad基准</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>差值(基准-当前)</t>
-        </is>
+          <t>总卡牌数</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="n">
+        <v>91</v>
+      </c>
+      <c r="C1" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="D1" s="10" t="n">
+        <v>-4</v>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>对比 IroncladCardPool 实际卡量</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="9">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>总卡牌数</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="C2" s="14" t="n">
-        <v>87</v>
-      </c>
-      <c r="D2" s="14" t="n">
-        <v>62</v>
-      </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>基于 IroncladCardPool 实际卡池</t>
-        </is>
-      </c>
+          <t>类型分布</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="9">
-      <c r="A3" s="14" t="n"/>
-      <c r="B3" s="14" t="n"/>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="E3" s="14" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="9">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>按类型</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="n"/>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>-4</v>
+      </c>
       <c r="E4" s="15" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="9">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>26</v>
+        <v>-2</v>
       </c>
       <c r="E5" s="14" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="9">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>21</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>19</v>
-      </c>
+          <t>稀有度分布</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
       <c r="E6" s="14" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="9">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Ancient</t>
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E7" s="14" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="9">
-      <c r="A8" s="14" t="n"/>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" s="14" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>按稀有度</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>-3</v>
+      </c>
       <c r="E9" s="15" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="9">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Ancient</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E10" s="14" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="9">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E11" s="14" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="9">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>12</v>
-      </c>
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
       <c r="E12" s="14" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="9">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>26</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>19</v>
-      </c>
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
       <c r="E13" s="14" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="9">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>36</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>29</v>
-      </c>
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
       <c r="E14" s="14" t="n"/>
     </row>
+    <row r="15"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2096,13 +2077,13 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>13</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="9">
@@ -2117,13 +2098,13 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>7</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="9">
@@ -2138,13 +2119,13 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>15</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="9">
@@ -2201,13 +2182,13 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="9">
@@ -2222,13 +2203,13 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>11</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="9">
@@ -2243,13 +2224,13 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>9</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="9">
@@ -2306,13 +2287,13 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>7</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="9">
@@ -2327,13 +2308,13 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>8</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="9">
@@ -2348,13 +2329,13 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>12</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5976,7 +5957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14.56" customWidth="1" style="8" min="1" max="1"/>
@@ -7086,13 +7067,17 @@
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>（效果未实现）</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr"/>
+          <t>对所有敌人造成10点伤害。将敌人身上的灼热层数翻倍。升级：造成14点伤害。</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>灼热/AOE</t>
+        </is>
+      </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>占位</t>
+          <t>焦土战术</t>
         </is>
       </c>
     </row>
@@ -7731,6 +7716,2661 @@
       <c r="G64" s="13" t="n"/>
       <c r="H64" s="13" t="n"/>
       <c r="I64" s="13" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>ATT_COM_06</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>EnergyOverload</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>能量超载</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>获得2点能量。赋予自身2层灼热。升级：获得3点能量。</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>灼热/能量</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>透支未来</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>ATT_COM_07</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>TimeDelayBurst</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>偏时迸发</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>本回合你的下一张攻击牌无视敌人格挡。升级：本回合所有攻击牌无视格挡。</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>破甲</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>无视防御</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>ATT_COM_08</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Breakthrough</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>突破</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>失去5点生命值。对所有敌人造成12点伤害。升级：造成18点伤害。</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>自伤/AOE</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>格拉默突击</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>ATT_COM_09</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>GrappleStrike</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>擒拿斩</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>造成8点伤害。如果本回合造成过伤害，伤害+4。升级：伤害+6。</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>连击</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>萨姆近战</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>ATT_COM_10</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>QuickStrike</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>迅捷斩</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>造成4点伤害。抽1张牌。升级：造成7点伤害。</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>过牌</t>
+        </is>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>快速攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>ATT_COM_11</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>HeavyBlow</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>重击</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>造成14点伤害。如果目标有灼热，伤害+6。升级：伤害+9。</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>灼热/高伤</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>灼热联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>ATT_COM_12</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>ScorchingBlade</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>灼热之刃</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>造成6点伤害。施加3层灼热。升级：造成9点伤害，施加4层灼热。</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>灼热</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>灼热叠加</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>ATT_COM_13</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>DissolutionWave</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>裂解波动</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>对所有敌人造成6点伤害。对所有有格挡的敌人赋予裂解。升级：造成9点伤害。</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>裂解/AOE</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>裂解体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>ATT_UNC_06</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Devastator</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>毁灭者</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>造成26点伤害。升级：造成34点伤害。</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>高伤</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>SAM重击</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>ATT_UNC_07</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>RisingFlame</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>升腾之焰</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>造成5点伤害。每层灼热使伤害+2。升级：每层灼热使伤害+3。</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>灼热/成长</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>灼热联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>ATT_UNC_08</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>FireflySwarm</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>萤火群舞</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>[萤火]造成5点伤害3次。激发：造成10点伤害3次，费用1。升级：造成7/14点伤害。</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>萤火/连击</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>萤火群攻</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>ATT_UNC_09</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>PrecisionStrike</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>精准打击</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>造成9点伤害。如果目标有裂解，抽1张牌。升级：抽2张牌。</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>裂解/过牌</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>裂解联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>ATT_UNC_10</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>EntropyBlade</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>熵之刃</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>造成10点伤害。移除目标所有格挡，每移除1点格挡造成2点伤害。升级：每点格挡造成3点伤害。</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>裂解/格挡</t>
+        </is>
+      </c>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>裂解体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>ATT_UNC_11</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>LifeBurning</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>燃命</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>失去等于当前能量值的生命值。造成等于失去生命值×2的伤害。升级：×3倍伤害。</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>自伤/高伤</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>生命燃烧</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>ATT_UNC_12</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>ScatterFlame</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>散焰</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>对所有敌人造成8点伤害。如果有敌人在灼热状态，额外施加2层灼热。升级：造成12点伤害。</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>灼热/AOE</t>
+        </is>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>灼热扩散</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>ATT_UNC_13</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>QuickDissolution</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>快速裂解</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>造成6点伤害。赋予目标裂解。如果目标已有裂解，改为造成12点伤害。升级：造成9/18点伤害。</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>裂解</t>
+        </is>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>裂解体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>ATT_UNC_14</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>FireflyNova</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>萤火新星</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>[萤火]对所有敌人造成7点伤害。激发：造成14点伤害，费用1。升级：造成10/20点伤害。</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>萤火/AOE</t>
+        </is>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>萤火爆发</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>ATT_UNC_15</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>RecklessCharge</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>莽撞冲锋</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>失去3点生命值。造成10点伤害。如果目标死于这张牌，回复3点生命值。升级：造成14点伤害。</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>自伤</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>格拉默冲锋</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>ATT_RAR_03</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>StarfireAnnihilation</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>星火湮灭</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>[萤火]造成25点伤害。激发：造成50点伤害，施加5层灼热，费用1。升级：造成33/66点伤害。</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>萤火/爆发</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>萤火终结技</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>ATT_RAR_04</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>OmegaBlaster</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>欧米伽爆破</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>消耗。对所有敌人造成20点伤害。施加5层灼热。升级：造成28点伤害，施加7层灼热。</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>灼热/AOE</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>消耗牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>ATT_RAR_05</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>FatalTrigger</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>致命触发</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>造成4点伤害。如果目标生命值低于25%，伤害变为3倍。升级：伤害变为4倍。</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>收割</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>斩杀</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>ATT_RAR_06</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>DissolutionAnnihilation</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>裂解湮灭</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>对所有拥有裂解的敌人造成15点伤害。每有一个裂解敌人，获得3点格挡。升级：造成21点伤害。</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>裂解/AOE</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>裂解收割</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>ATT_RAR_07</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>LastLight</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>最后之光</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>生命值低于10点时才能打出。对所有敌人造成等于当前生命值的伤害。升级：伤害+10。</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>绝境/爆发</t>
+        </is>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>萤火虫最后光芒</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>SKI_COM_05</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>EnergyBoost</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>能量激增</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>获得1点能量。抽1张牌。升级：获得2点能量。</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>能量/过牌</t>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>快速充能</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>SKI_COM_06</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>ReinforcedArmor</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>强化装甲</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>获得12点格挡。如果你的生命值低于50%，额外获得6点格挡。升级：获得16点格挡。</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>格挡/生存</t>
+        </is>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>SAM装甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>SKI_COM_07</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>DesperateDefense</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>绝境防御</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>获得5点格挡。生命值每低于最大值10点，格挡+2。升级：格挡+3。</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>格挡/生存</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>低血量加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>SKI_COM_08</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>EmergencyRepair</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>紧急修复</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>失去2点生命值。获得8点格挡。抽1张牌。升级：获得12点格挡。</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>自伤/格挡</t>
+        </is>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>快速修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>SKI_UNC_04</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>FireflyDance</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>萤火之舞</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>抽2张牌。本回合你打出的下一张攻击牌费用为0。升级：抽3张牌。</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>过牌/减费</t>
+        </is>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>快速连击</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>SKI_UNC_05</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>ScorchAbsorb</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>灼热吸收</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>移除一个敌人身上的所有灼热。每移除1层，回复2点生命值。升级：回复3点生命值。</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>灼热/回复</t>
+        </is>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>灼热转化</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>SKI_UNC_06</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>BarrierTransfer</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>屏障转移</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>将目标敌人身上的所有格挡转移给自己。升级：转移的格挡+50%。</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>裂解/格挡</t>
+        </is>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>裂解体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>SKI_UNC_07</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>FireflySpark</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>萤火迸发</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>[萤火]激发手牌中一张萤火牌。升级：激发所有萤火牌。</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>萤火/激发</t>
+        </is>
+      </c>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>萤火辅助</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>SKI_UNC_08</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>TacticalRetreat</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>战术撤退</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>获得6点格挡。将手牌中所有萤火牌置入弃牌堆，每张抽1张牌。升级：获得9点格挡。</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>萤火/过牌</t>
+        </is>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>萤火循环</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>SKI_UNC_09</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>DissolutionField</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>裂解力场</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>对所有敌人赋予裂解。获得等于敌人数量×3的格挡。升级：获得×5的格挡。</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>裂解/防御</t>
+        </is>
+      </c>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>裂解体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>SKI_UNC_10</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>BurningSpirit</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>燃烧意志</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>失去4点生命值。本回合获得2层力量。升级：获得3层力量。</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>自伤/力量</t>
+        </is>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>燃烧增益</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>SKI_UNC_11</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>EntropyShield</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>熵之盾</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>获得等于当前失去生命值一半的格挡。升级：获得等于失去生命值的格挡。</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>格挡/生存</t>
+        </is>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>低血量加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>SKI_UNC_12</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>QuickIgnition</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>快速点燃</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>选择手牌中一张牌，使其获得萤火属性。抽1张牌。升级：抽2张牌。</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>萤火/过牌</t>
+        </is>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>萤火赋予</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>SKI_RAR_04</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>LifeWhySleep</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>生命因何而沉睡</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>生命值上限减少10点。本场战斗获得3点能量。升级：减少8点，获得4点能量。</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>风险/能量</t>
+        </is>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>哲学命题</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>SKI_RAR_05</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>FireflyCycle</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>萤火循环</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>将弃牌堆中所有萤火牌返回手牌。获得等于返回数量×2的格挡。升级：获得×3格挡。</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>萤火/循环</t>
+        </is>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>萤火回收</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>SKI_RAR_06</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>TimeStop</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>时停</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>本回合敌人不行动。你受到的所有伤害+5。消耗。升级：受到伤害+3。</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>控制/风险</t>
+        </is>
+      </c>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>时间停止</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>SKI_RAR_07</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>OmeletCake</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>橡木蛋糕卷</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>回复15点生命值。获得1点能量。每场战斗限用1次。升级：回复20点生命值，获得2点能量。</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>回复/能量</t>
+        </is>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>流萤最爱</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>SKI_RAR_08</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>RooftopPhoto</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>天台合影</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>获得8点格挡。抽1张牌。如果手牌中有萤火牌，额外获得4点格挡。升级：获得12点格挡，抽2张牌。</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>格挡/过牌</t>
+        </is>
+      </c>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t>美好回忆</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>POW_UNC_03</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>ThermalReaction</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>热核反应</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>每当你施加灼热，获得1点格挡。升级：获得2点格挡。</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>灼热/格挡</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>灼热联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>POW_UNC_04</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>BurningWill</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>燃烧意志</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>生命值低于50%时，伤害+2。升级：伤害+3。</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>自伤/力量</t>
+        </is>
+      </c>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>低血量增益</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>POW_UNC_05</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>FireflyResonance</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>萤火共鸣</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>萤火牌激发时，额外获得1点能量。升级：获得2点能量。</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>萤火/能量</t>
+        </is>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>萤火增益</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>POW_UNC_06</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>BlockMastery</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>格挡精通</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>从卡牌获得的格挡+3。升级：格挡+5。</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>格挡</t>
+        </is>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>防御强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>POW_UNC_07</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>ScorchMastery</t>
+        </is>
+      </c>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>灼热精通</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>施加的灼热层数+1。升级：灼热层数+2。</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>灼热</t>
+        </is>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>灼热强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>POW_UNC_08</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>DissolutionResonance</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>裂解共鸣</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>触发裂解伤害时，额外造成等于伤害值20%的伤害。升级：30%额外伤害。</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>裂解</t>
+        </is>
+      </c>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>裂解强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>POW_UNC_09</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>LifeExchange</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>生命交换</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>回合开始时，失去2点生命值，获得1层力量。升级：失去1点生命值。</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>自伤/力量</t>
+        </is>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>生命转化</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>POW_UNC_10</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>FireflyMemory</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>萤火记忆</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>萤火牌被打出后，有50%概率返回手牌。升级：75%概率。</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>萤火/循环</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>萤火回收</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>POW_UNC_11</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>ArmorBreaker</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>破甲专家</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>你造成的伤害对格挡额外造成50%伤害。升级：额外造成100%伤害。</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>裂解/破甲</t>
+        </is>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>裂解体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>POW_RAR_04</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>ThreeDeaths</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>三次死亡</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>本场战斗限3次：当你生命值降至1时，获得无敌1回合并抽2张牌。升级：获得无敌2回合。</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>生存/复活</t>
+        </is>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>流萤命运</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>POW_RAR_05</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>FireflyNest</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>萤火之巢</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>回合结束时，将手牌中一张随机非萤火牌变为萤火牌。升级：变2张。</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>萤火/转化</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>萤火生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>POW_RAR_06</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>Inferno</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>地狱火</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>灼热触发时，有50%概率不减少层数。升级：75%概率。</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>灼热/持续</t>
+        </is>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>灼热增强</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>POW_RAR_07</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>EntropyMaster</t>
+        </is>
+      </c>
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t>熵之主宰</t>
+        </is>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>每当你赋予裂解，获得1点能量。升级：获得2点能量。</t>
+        </is>
+      </c>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>裂解/能量</t>
+        </is>
+      </c>
+      <c r="I118" s="8" t="inlineStr">
+        <is>
+          <t>裂解体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>POW_RAR_08</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>LastStand</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>背水一战</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>生命值低于20点时，攻击牌耗能-1。升级：生命值低于25点时生效。</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>自伤/减费</t>
+        </is>
+      </c>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>低血量增益</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>POW_RAR_09</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>FireflyBlessing</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>萤火祝福</t>
+        </is>
+      </c>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>萤火牌激发时效果额外+50%。升级：效果+100%。</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>萤火/增强</t>
+        </is>
+      </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>萤火核心</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>POW_RAR_10</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>PhoenixRise</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>凤凰涅槃</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>本场战斗第一次死亡时，以50%生命值复活，激发所有手牌中的萤火牌。升级：以75%生命值复活。</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>生存/复活</t>
+        </is>
+      </c>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t>重生</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>POW_RAR_11</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>ScorchAura</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="inlineStr">
+        <is>
+          <t>灼热光环</t>
+        </is>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>回合开始时，对有灼热的敌人造成等同于灼热层数50%的伤害。升级：造成75%伤害。</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>灼热</t>
+        </is>
+      </c>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>灼热增强</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>POW_RAR_12</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>DissolutionCore</t>
+        </is>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>裂解核心</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>裂解伤害翻倍。升级：裂解伤害×3。</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>裂解</t>
+        </is>
+      </c>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>裂解核心</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/docs/firefly_card_benchmark_template.xlsx
+++ b/docs/firefly_card_benchmark_template.xlsx
@@ -1767,7 +1767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.38" customWidth="1" style="8" min="1" max="1"/>
@@ -1975,7 +1975,6 @@
       <c r="D14" s="14" t="n"/>
       <c r="E14" s="14" t="n"/>
     </row>
-    <row r="15"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6055,7 +6054,7 @@
           <t>初始/攻击</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr"/>
+      <c r="I2" s="13" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="9">
       <c r="A3" s="12" t="inlineStr">
@@ -6096,7 +6095,7 @@
           <t>自伤/高伤</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr"/>
+      <c r="I3" s="13" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="9">
       <c r="A4" s="12" t="inlineStr">
@@ -6137,7 +6136,7 @@
           <t>连击/灼热</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr"/>
+      <c r="I4" s="13" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="9">
       <c r="A5" s="12" t="inlineStr">
@@ -6178,7 +6177,7 @@
           <t>萤火/激发</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr"/>
+      <c r="I5" s="13" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="9">
       <c r="A6" s="12" t="inlineStr">
@@ -6309,7 +6308,7 @@
           <t>攻击</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="9">
       <c r="A9" s="12" t="inlineStr">
@@ -6395,7 +6394,7 @@
           <t>攻击/灼热</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="9">
       <c r="A11" s="12" t="inlineStr">
@@ -6436,7 +6435,7 @@
           <t>自伤/高伤</t>
         </is>
       </c>
-      <c r="I11" s="13" t="inlineStr"/>
+      <c r="I11" s="13" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="9">
       <c r="A12" s="12" t="inlineStr">
@@ -6477,7 +6476,7 @@
           <t>萤火/力量</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="9">
       <c r="A13" s="12" t="inlineStr">
@@ -6518,7 +6517,7 @@
           <t>高伤/回复</t>
         </is>
       </c>
-      <c r="I13" s="13" t="inlineStr"/>
+      <c r="I13" s="13" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="9">
       <c r="A14" s="12" t="inlineStr">
@@ -6604,7 +6603,7 @@
           <t>初始/防御</t>
         </is>
       </c>
-      <c r="I15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="9">
       <c r="A16" s="12" t="inlineStr">
@@ -6690,7 +6689,7 @@
           <t>萤火/防御</t>
         </is>
       </c>
-      <c r="I17" s="13" t="inlineStr"/>
+      <c r="I17" s="13" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="9">
       <c r="A18" s="12" t="inlineStr">
@@ -6776,7 +6775,7 @@
           <t>自伤/高格挡</t>
         </is>
       </c>
-      <c r="I19" s="13" t="inlineStr"/>
+      <c r="I19" s="13" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="9">
       <c r="A20" s="12" t="inlineStr">
@@ -6817,7 +6816,7 @@
           <t>格挡/自伤</t>
         </is>
       </c>
-      <c r="I20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="9">
       <c r="A21" s="12" t="inlineStr">
@@ -6858,7 +6857,7 @@
           <t>萤火/抽牌</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr"/>
+      <c r="I21" s="13" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="9">
       <c r="A22" s="12" t="inlineStr">
@@ -6944,7 +6943,7 @@
           <t>萤火/能量</t>
         </is>
       </c>
-      <c r="I23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="9">
       <c r="A24" s="12" t="inlineStr">
@@ -7120,7 +7119,7 @@
           <t>荆棘/保命</t>
         </is>
       </c>
-      <c r="I27" s="13" t="inlineStr"/>
+      <c r="I27" s="13" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="9">
       <c r="A28" s="12" t="inlineStr">
@@ -7161,7 +7160,7 @@
           <t>自伤/力量</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="9">
       <c r="A29" s="12" t="inlineStr">
@@ -7202,7 +7201,7 @@
           <t>抽牌</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr"/>
+      <c r="I29" s="13" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="9">
       <c r="A30" s="12" t="inlineStr">
@@ -7243,7 +7242,7 @@
           <t>减伤</t>
         </is>
       </c>
-      <c r="I30" s="13" t="inlineStr"/>
+      <c r="I30" s="13" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="9">
       <c r="A31" s="12" t="inlineStr">
@@ -7374,363 +7373,1417 @@
           <t>灼热/持续</t>
         </is>
       </c>
-      <c r="I33" s="13" t="inlineStr"/>
+      <c r="I33" s="13" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="9">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>ATT_COM_06</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>EnergyOverload</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>能量超载</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>获得2点能量。赋予自身2层灼热。升级：获得3点能量。</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>灼热/能量</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>透支未来</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="9">
-      <c r="A35" s="12" t="n"/>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>ATT_COM_07</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>TimeDelayBurst</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>偏时迸发</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>本回合你的下一张攻击牌无视敌人格挡。升级：本回合所有攻击牌无视格挡。</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>破甲</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>无视防御</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="9">
-      <c r="A36" s="12" t="n"/>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="13" t="n"/>
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>ATT_COM_08</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>Breakthrough</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>突破</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>失去5点生命值。对所有敌人造成12点伤害。升级：造成18点伤害。</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>自伤/AOE</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>格拉默突击</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="9">
-      <c r="A37" s="12" t="n"/>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>ATT_COM_09</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>GrappleStrike</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>擒拿斩</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>造成8点伤害。如果本回合造成过伤害，伤害+4。升级：伤害+6。</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>连击</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>萨姆近战</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="9">
-      <c r="A38" s="12" t="n"/>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="13" t="n"/>
-      <c r="H38" s="13" t="n"/>
-      <c r="I38" s="13" t="n"/>
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>ATT_COM_10</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>QuickStrike</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>迅捷斩</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>造成4点伤害。抽1张牌。升级：造成7点伤害。</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>过牌</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>快速攻击</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="9">
-      <c r="A39" s="12" t="n"/>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="13" t="n"/>
-      <c r="H39" s="13" t="n"/>
-      <c r="I39" s="13" t="n"/>
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>ATT_COM_11</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>HeavyBlow</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>重击</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>造成14点伤害。如果目标有灼热，伤害+6。升级：伤害+9。</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>灼热/高伤</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>灼热联动</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="9">
-      <c r="A40" s="12" t="n"/>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="13" t="n"/>
-      <c r="H40" s="13" t="n"/>
-      <c r="I40" s="13" t="n"/>
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>ATT_COM_12</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>ScorchingBlade</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>灼热之刃</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>造成6点伤害。施加3层灼热。升级：造成9点伤害，施加4层灼热。</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>灼热</t>
+        </is>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>灼热叠加</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="9">
-      <c r="A41" s="12" t="n"/>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="13" t="n"/>
-      <c r="H41" s="13" t="n"/>
-      <c r="I41" s="13" t="n"/>
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>ATT_COM_13</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>DissolutionWave</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>裂解波动</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>对所有敌人造成6点伤害。对所有有格挡的敌人赋予裂解。升级：造成9点伤害。</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>裂解/AOE</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>裂解体系</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="9">
-      <c r="A42" s="12" t="n"/>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="13" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="13" t="n"/>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>ATT_UNC_06</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Devastator</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>毁灭者</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>造成26点伤害。升级：造成34点伤害。</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>高伤</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>SAM重击</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="9">
-      <c r="A43" s="12" t="n"/>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="13" t="n"/>
-      <c r="H43" s="13" t="n"/>
-      <c r="I43" s="13" t="n"/>
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>ATT_UNC_07</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>RisingFlame</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>升腾之焰</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>造成5点伤害。每层灼热使伤害+2。升级：每层灼热使伤害+3。</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>灼热/成长</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>灼热联动</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="9">
-      <c r="A44" s="12" t="n"/>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
-      <c r="I44" s="13" t="n"/>
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>ATT_UNC_08</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>FireflySwarm</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>萤火群舞</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>[萤火]造成5点伤害3次。激发：造成10点伤害3次，费用1。升级：造成7/14点伤害。</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>萤火/连击</t>
+        </is>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>萤火群攻</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="9">
-      <c r="A45" s="12" t="n"/>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="13" t="n"/>
-      <c r="H45" s="13" t="n"/>
-      <c r="I45" s="13" t="n"/>
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>ATT_UNC_09</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>PrecisionStrike</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>精准打击</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>造成9点伤害。如果目标有裂解，抽1张牌。升级：抽2张牌。</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>裂解/过牌</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>裂解联动</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="9">
-      <c r="A46" s="12" t="n"/>
-      <c r="B46" s="12" t="n"/>
-      <c r="C46" s="12" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="13" t="n"/>
-      <c r="H46" s="13" t="n"/>
-      <c r="I46" s="13" t="n"/>
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>ATT_UNC_10</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>EntropyBlade</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>熵之刃</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>造成10点伤害。移除目标所有格挡，每移除1点格挡造成2点伤害。升级：每点格挡造成3点伤害。</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>裂解/格挡</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>裂解体系</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="9">
-      <c r="A47" s="12" t="n"/>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="13" t="n"/>
-      <c r="H47" s="13" t="n"/>
-      <c r="I47" s="13" t="n"/>
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>ATT_UNC_11</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>LifeBurning</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>燃命</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>失去等于当前能量值的生命值。造成等于失去生命值×2的伤害。升级：×3倍伤害。</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>自伤/高伤</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>生命燃烧</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="9">
-      <c r="A48" s="12" t="n"/>
-      <c r="B48" s="12" t="n"/>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="13" t="n"/>
-      <c r="E48" s="13" t="n"/>
-      <c r="F48" s="13" t="n"/>
-      <c r="G48" s="13" t="n"/>
-      <c r="H48" s="13" t="n"/>
-      <c r="I48" s="13" t="n"/>
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>ATT_UNC_12</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>ScatterFlame</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>散焰</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>对所有敌人造成8点伤害。如果有敌人在灼热状态，额外施加2层灼热。升级：造成12点伤害。</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>灼热/AOE</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>灼热扩散</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="9">
-      <c r="A49" s="12" t="n"/>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="13" t="n"/>
-      <c r="G49" s="13" t="n"/>
-      <c r="H49" s="13" t="n"/>
-      <c r="I49" s="13" t="n"/>
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>ATT_UNC_13</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>QuickDissolution</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>快速裂解</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>造成6点伤害。赋予目标裂解。如果目标已有裂解，改为造成12点伤害。升级：造成9/18点伤害。</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>裂解</t>
+        </is>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>裂解体系</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="9">
-      <c r="A50" s="12" t="n"/>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="13" t="n"/>
-      <c r="H50" s="13" t="n"/>
-      <c r="I50" s="13" t="n"/>
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>ATT_UNC_14</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>FireflyNova</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>萤火新星</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>[萤火]对所有敌人造成7点伤害。激发：造成14点伤害，费用1。升级：造成10/20点伤害。</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>萤火/AOE</t>
+        </is>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>萤火爆发</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="9">
-      <c r="A51" s="12" t="n"/>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="13" t="n"/>
-      <c r="E51" s="13" t="n"/>
-      <c r="F51" s="13" t="n"/>
-      <c r="G51" s="13" t="n"/>
-      <c r="H51" s="13" t="n"/>
-      <c r="I51" s="13" t="n"/>
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>ATT_UNC_15</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>RecklessCharge</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>莽撞冲锋</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>失去3点生命值。造成10点伤害。如果目标死于这张牌，回复3点生命值。升级：造成14点伤害。</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>自伤</t>
+        </is>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>格拉默冲锋</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="9">
-      <c r="A52" s="12" t="n"/>
-      <c r="B52" s="12" t="n"/>
-      <c r="C52" s="12" t="n"/>
-      <c r="D52" s="13" t="n"/>
-      <c r="E52" s="13" t="n"/>
-      <c r="F52" s="13" t="n"/>
-      <c r="G52" s="13" t="n"/>
-      <c r="H52" s="13" t="n"/>
-      <c r="I52" s="13" t="n"/>
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>ATT_RAR_03</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>StarfireAnnihilation</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>星火湮灭</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>[萤火]造成25点伤害。激发：造成50点伤害，施加5层灼热，费用1。升级：造成33/66点伤害。</t>
+        </is>
+      </c>
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>萤火/爆发</t>
+        </is>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>萤火终结技</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="9">
-      <c r="A53" s="12" t="n"/>
-      <c r="B53" s="12" t="n"/>
-      <c r="C53" s="12" t="n"/>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="13" t="n"/>
-      <c r="G53" s="13" t="n"/>
-      <c r="H53" s="13" t="n"/>
-      <c r="I53" s="13" t="n"/>
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>ATT_RAR_04</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>OmegaBlaster</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>欧米伽爆破</t>
+        </is>
+      </c>
+      <c r="G53" s="13" t="inlineStr">
+        <is>
+          <t>消耗。对所有敌人造成20点伤害。施加5层灼热。升级：造成28点伤害，施加7层灼热。</t>
+        </is>
+      </c>
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t>灼热/AOE</t>
+        </is>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>消耗牌</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="9">
-      <c r="A54" s="12" t="n"/>
-      <c r="B54" s="12" t="n"/>
-      <c r="C54" s="12" t="n"/>
-      <c r="D54" s="13" t="n"/>
-      <c r="E54" s="13" t="n"/>
-      <c r="F54" s="13" t="n"/>
-      <c r="G54" s="13" t="n"/>
-      <c r="H54" s="13" t="n"/>
-      <c r="I54" s="13" t="n"/>
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>ATT_RAR_05</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>FatalTrigger</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
+        <is>
+          <t>致命触发</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>造成4点伤害。如果目标生命值低于25%，伤害变为3倍。升级：伤害变为4倍。</t>
+        </is>
+      </c>
+      <c r="H54" s="13" t="inlineStr">
+        <is>
+          <t>收割</t>
+        </is>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>斩杀</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="9">
-      <c r="A55" s="12" t="n"/>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
-      <c r="G55" s="13" t="n"/>
-      <c r="H55" s="13" t="n"/>
-      <c r="I55" s="13" t="n"/>
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>ATT_RAR_06</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>DissolutionAnnihilation</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>裂解湮灭</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>对所有拥有裂解的敌人造成15点伤害。每有一个裂解敌人，获得3点格挡。升级：造成21点伤害。</t>
+        </is>
+      </c>
+      <c r="H55" s="13" t="inlineStr">
+        <is>
+          <t>裂解/AOE</t>
+        </is>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>裂解收割</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="9">
-      <c r="A56" s="12" t="n"/>
-      <c r="B56" s="12" t="n"/>
-      <c r="C56" s="12" t="n"/>
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
-      <c r="G56" s="13" t="n"/>
-      <c r="H56" s="13" t="n"/>
-      <c r="I56" s="13" t="n"/>
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>ATT_RAR_07</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>LastLight</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="inlineStr">
+        <is>
+          <t>最后之光</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>生命值低于10点时才能打出。对所有敌人造成等于当前生命值的伤害。升级：伤害+10。</t>
+        </is>
+      </c>
+      <c r="H56" s="13" t="inlineStr">
+        <is>
+          <t>绝境/爆发</t>
+        </is>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>萤火虫最后光芒</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="9">
-      <c r="A57" s="12" t="n"/>
-      <c r="B57" s="12" t="n"/>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
-      <c r="F57" s="13" t="n"/>
-      <c r="G57" s="13" t="n"/>
-      <c r="H57" s="13" t="n"/>
-      <c r="I57" s="13" t="n"/>
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>SKI_COM_05</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>EnergyBoost</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>能量激增</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>获得1点能量。抽1张牌。升级：获得2点能量。</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>能量/过牌</t>
+        </is>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>快速充能</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="9">
-      <c r="A58" s="12" t="n"/>
-      <c r="B58" s="12" t="n"/>
-      <c r="C58" s="12" t="n"/>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
-      <c r="G58" s="13" t="n"/>
-      <c r="H58" s="13" t="n"/>
-      <c r="I58" s="13" t="n"/>
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>SKI_COM_06</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>ReinforcedArmor</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>强化装甲</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>获得12点格挡。如果你的生命值低于50%，额外获得6点格挡。升级：获得16点格挡。</t>
+        </is>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>格挡/生存</t>
+        </is>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>SAM装甲</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="9">
-      <c r="A59" s="12" t="n"/>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="13" t="n"/>
-      <c r="E59" s="13" t="n"/>
-      <c r="F59" s="13" t="n"/>
-      <c r="G59" s="13" t="n"/>
-      <c r="H59" s="13" t="n"/>
-      <c r="I59" s="13" t="n"/>
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>SKI_COM_07</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>DesperateDefense</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>绝境防御</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>获得5点格挡。生命值每低于最大值10点，格挡+2。升级：格挡+3。</t>
+        </is>
+      </c>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>格挡/生存</t>
+        </is>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>低血量加成</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="9">
-      <c r="A60" s="12" t="n"/>
-      <c r="B60" s="12" t="n"/>
-      <c r="C60" s="12" t="n"/>
-      <c r="D60" s="13" t="n"/>
-      <c r="E60" s="13" t="n"/>
-      <c r="F60" s="13" t="n"/>
-      <c r="G60" s="13" t="n"/>
-      <c r="H60" s="13" t="n"/>
-      <c r="I60" s="13" t="n"/>
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>SKI_COM_08</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>EmergencyRepair</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>紧急修复</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>失去2点生命值。获得8点格挡。抽1张牌。升级：获得12点格挡。</t>
+        </is>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>自伤/格挡</t>
+        </is>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>快速修复</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="9">
-      <c r="A61" s="12" t="n"/>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="13" t="n"/>
-      <c r="E61" s="13" t="n"/>
-      <c r="F61" s="13" t="n"/>
-      <c r="G61" s="13" t="n"/>
-      <c r="H61" s="13" t="n"/>
-      <c r="I61" s="13" t="n"/>
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>SKI_UNC_04</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>FireflyDance</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>萤火之舞</t>
+        </is>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>抽2张牌。本回合你打出的下一张攻击牌费用为0。升级：抽3张牌。</t>
+        </is>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>过牌/减费</t>
+        </is>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>快速连击</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="9">
-      <c r="A62" s="12" t="n"/>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="13" t="n"/>
-      <c r="G62" s="13" t="n"/>
-      <c r="H62" s="13" t="n"/>
-      <c r="I62" s="13" t="n"/>
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>SKI_UNC_05</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>ScorchAbsorb</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>灼热吸收</t>
+        </is>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>移除一个敌人身上的所有灼热。每移除1层，回复2点生命值。升级：回复3点生命值。</t>
+        </is>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>灼热/回复</t>
+        </is>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>灼热转化</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="9">
-      <c r="A63" s="12" t="n"/>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="12" t="n"/>
-      <c r="D63" s="13" t="n"/>
-      <c r="E63" s="13" t="n"/>
-      <c r="F63" s="13" t="n"/>
-      <c r="G63" s="13" t="n"/>
-      <c r="H63" s="13" t="n"/>
-      <c r="I63" s="13" t="n"/>
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>SKI_UNC_06</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>BarrierTransfer</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>屏障转移</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>将目标敌人身上的所有格挡转移给自己。升级：转移的格挡+50%。</t>
+        </is>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>裂解/格挡</t>
+        </is>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>裂解体系</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="9">
-      <c r="A64" s="12" t="n"/>
-      <c r="B64" s="12" t="n"/>
-      <c r="C64" s="12" t="n"/>
-      <c r="D64" s="13" t="n"/>
-      <c r="E64" s="13" t="n"/>
-      <c r="F64" s="13" t="n"/>
-      <c r="G64" s="13" t="n"/>
-      <c r="H64" s="13" t="n"/>
-      <c r="I64" s="13" t="n"/>
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>SKI_UNC_07</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>FireflySpark</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>萤火迸发</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>[萤火]激发手牌中一张萤火牌。升级：激发所有萤火牌。</t>
+        </is>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>萤火/激发</t>
+        </is>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>萤火辅助</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>ATT_COM_06</t>
+          <t>SKI_UNC_08</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D65" s="8" t="n">
@@ -7738,269 +8791,269 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>EnergyOverload</t>
+          <t>TacticalRetreat</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>能量超载</t>
+          <t>战术撤退</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>获得2点能量。赋予自身2层灼热。升级：获得3点能量。</t>
+          <t>获得6点格挡。将手牌中所有萤火牌置入弃牌堆，每张抽1张牌。升级：获得9点格挡。</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>灼热/能量</t>
+          <t>萤火/过牌</t>
         </is>
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>透支未来</t>
+          <t>萤火循环</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>ATT_COM_07</t>
+          <t>SKI_UNC_09</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>TimeDelayBurst</t>
+          <t>DissolutionField</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>偏时迸发</t>
+          <t>裂解力场</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>本回合你的下一张攻击牌无视敌人格挡。升级：本回合所有攻击牌无视格挡。</t>
+          <t>对所有敌人赋予裂解。获得等于敌人数量×3的格挡。升级：获得×5的格挡。</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>破甲</t>
+          <t>裂解/防御</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>无视防御</t>
+          <t>裂解体系</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>ATT_COM_08</t>
+          <t>SKI_UNC_10</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Breakthrough</t>
+          <t>BurningSpirit</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>突破</t>
+          <t>燃烧意志</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>失去5点生命值。对所有敌人造成12点伤害。升级：造成18点伤害。</t>
+          <t>失去4点生命值。本回合获得2层力量。升级：获得3层力量。</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>自伤/AOE</t>
+          <t>自伤/力量</t>
         </is>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>格拉默突击</t>
+          <t>燃烧增益</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>ATT_COM_09</t>
+          <t>SKI_UNC_11</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>GrappleStrike</t>
+          <t>EntropyShield</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>擒拿斩</t>
+          <t>熵之盾</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>造成8点伤害。如果本回合造成过伤害，伤害+4。升级：伤害+6。</t>
+          <t>获得等于当前失去生命值一半的格挡。升级：获得等于失去生命值的格挡。</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>连击</t>
+          <t>格挡/生存</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>萨姆近战</t>
+          <t>低血量加成</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>ATT_COM_10</t>
+          <t>SKI_UNC_12</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>QuickStrike</t>
+          <t>QuickIgnition</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>迅捷斩</t>
+          <t>快速点燃</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>造成4点伤害。抽1张牌。升级：造成7点伤害。</t>
+          <t>选择手牌中一张牌，使其获得萤火属性。抽1张牌。升级：抽2张牌。</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>过牌</t>
+          <t>萤火/过牌</t>
         </is>
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>快速攻击</t>
+          <t>萤火赋予</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>ATT_COM_11</t>
+          <t>SKI_RAR_04</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>HeavyBlow</t>
+          <t>LifeWhySleep</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>重击</t>
+          <t>生命因何而沉睡</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>造成14点伤害。如果目标有灼热，伤害+6。升级：伤害+9。</t>
+          <t>生命值上限减少10点。本场战斗获得3点能量。升级：减少8点，获得4点能量。</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>灼热/高伤</t>
+          <t>风险/能量</t>
         </is>
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>灼热联动</t>
+          <t>哲学命题</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>ATT_COM_12</t>
+          <t>SKI_RAR_05</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D71" s="8" t="n">
@@ -8008,134 +9061,134 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>ScorchingBlade</t>
+          <t>FireflyCycle</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>灼热之刃</t>
+          <t>萤火循环</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>造成6点伤害。施加3层灼热。升级：造成9点伤害，施加4层灼热。</t>
+          <t>将弃牌堆中所有萤火牌返回手牌。获得等于返回数量×2的格挡。升级：获得×3格挡。</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>灼热</t>
+          <t>萤火/循环</t>
         </is>
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>灼热叠加</t>
+          <t>萤火回收</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>ATT_COM_13</t>
+          <t>SKI_RAR_06</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>DissolutionWave</t>
+          <t>TimeStop</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>裂解波动</t>
+          <t>时停</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>对所有敌人造成6点伤害。对所有有格挡的敌人赋予裂解。升级：造成9点伤害。</t>
+          <t>本回合敌人不行动。你受到的所有伤害+5。消耗。升级：受到伤害+3。</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>裂解/AOE</t>
+          <t>控制/风险</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>裂解体系</t>
+          <t>时间停止</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>ATT_UNC_06</t>
+          <t>SKI_RAR_07</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Devastator</t>
+          <t>OmeletCake</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>毁灭者</t>
+          <t>橡木蛋糕卷</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>造成26点伤害。升级：造成34点伤害。</t>
+          <t>回复15点生命值。获得1点能量。每场战斗限用1次。升级：回复20点生命值，获得2点能量。</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>高伤</t>
+          <t>回复/能量</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>SAM重击</t>
+          <t>流萤最爱</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>ATT_UNC_07</t>
+          <t>SKI_RAR_08</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
@@ -8143,39 +9196,39 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>RisingFlame</t>
+          <t>RooftopPhoto</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>升腾之焰</t>
+          <t>天台合影</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>造成5点伤害。每层灼热使伤害+2。升级：每层灼热使伤害+3。</t>
+          <t>获得8点格挡。抽1张牌。如果手牌中有萤火牌，额外获得4点格挡。升级：获得12点格挡，抽2张牌。</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>灼热/成长</t>
+          <t>格挡/过牌</t>
         </is>
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>灼热联动</t>
+          <t>美好回忆</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>ATT_UNC_08</t>
+          <t>POW_UNC_03</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -8184,43 +9237,43 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>FireflySwarm</t>
+          <t>ThermalReaction</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>萤火群舞</t>
+          <t>热核反应</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>[萤火]造成5点伤害3次。激发：造成10点伤害3次，费用1。升级：造成7/14点伤害。</t>
+          <t>每当你施加灼热，获得1点格挡。升级：获得2点格挡。</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>萤火/连击</t>
+          <t>灼热/格挡</t>
         </is>
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>萤火群攻</t>
+          <t>灼热联动</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>ATT_UNC_09</t>
+          <t>POW_UNC_04</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -8229,43 +9282,43 @@
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>PrecisionStrike</t>
+          <t>BurningWill</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>精准打击</t>
+          <t>燃烧意志</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>造成9点伤害。如果目标有裂解，抽1张牌。升级：抽2张牌。</t>
+          <t>生命值低于50%时，伤害+2。升级：伤害+3。</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>裂解/过牌</t>
+          <t>自伤/力量</t>
         </is>
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>裂解联动</t>
+          <t>低血量增益</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>ATT_UNC_10</t>
+          <t>POW_UNC_05</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -8274,43 +9327,43 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>EntropyBlade</t>
+          <t>FireflyResonance</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>熵之刃</t>
+          <t>萤火共鸣</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>造成10点伤害。移除目标所有格挡，每移除1点格挡造成2点伤害。升级：每点格挡造成3点伤害。</t>
+          <t>萤火牌激发时，额外获得1点能量。升级：获得2点能量。</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>裂解/格挡</t>
+          <t>萤火/能量</t>
         </is>
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>裂解体系</t>
+          <t>萤火增益</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>ATT_UNC_11</t>
+          <t>POW_UNC_06</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -8323,39 +9376,39 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>LifeBurning</t>
+          <t>BlockMastery</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>燃命</t>
+          <t>格挡精通</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>失去等于当前能量值的生命值。造成等于失去生命值×2的伤害。升级：×3倍伤害。</t>
+          <t>从卡牌获得的格挡+3。升级：格挡+5。</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>自伤/高伤</t>
+          <t>格挡</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>生命燃烧</t>
+          <t>防御强化</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>ATT_UNC_12</t>
+          <t>POW_UNC_07</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -8368,39 +9421,39 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>ScatterFlame</t>
+          <t>ScorchMastery</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>散焰</t>
+          <t>灼热精通</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>对所有敌人造成8点伤害。如果有敌人在灼热状态，额外施加2层灼热。升级：造成12点伤害。</t>
+          <t>施加的灼热层数+1。升级：灼热层数+2。</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>灼热/AOE</t>
+          <t>灼热</t>
         </is>
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>灼热扩散</t>
+          <t>灼热强化</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>ATT_UNC_13</t>
+          <t>POW_UNC_08</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -8413,17 +9466,17 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>QuickDissolution</t>
+          <t>DissolutionResonance</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>快速裂解</t>
+          <t>裂解共鸣</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>造成6点伤害。赋予目标裂解。如果目标已有裂解，改为造成12点伤害。升级：造成9/18点伤害。</t>
+          <t>触发裂解伤害时，额外造成等于伤害值20%的伤害。升级：30%额外伤害。</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -8433,19 +9486,19 @@
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>裂解体系</t>
+          <t>裂解强化</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>ATT_UNC_14</t>
+          <t>POW_UNC_09</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -8458,39 +9511,39 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>FireflyNova</t>
+          <t>LifeExchange</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>萤火新星</t>
+          <t>生命交换</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>[萤火]对所有敌人造成7点伤害。激发：造成14点伤害，费用1。升级：造成10/20点伤害。</t>
+          <t>回合开始时，失去2点生命值，获得1层力量。升级：失去1点生命值。</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>萤火/AOE</t>
+          <t>自伤/力量</t>
         </is>
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>萤火爆发</t>
+          <t>生命转化</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>ATT_UNC_15</t>
+          <t>POW_UNC_10</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -8503,44 +9556,44 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>RecklessCharge</t>
+          <t>FireflyMemory</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>莽撞冲锋</t>
+          <t>萤火记忆</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>失去3点生命值。造成10点伤害。如果目标死于这张牌，回复3点生命值。升级：造成14点伤害。</t>
+          <t>萤火牌被打出后，有50%概率返回手牌。升级：75%概率。</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>自伤</t>
+          <t>萤火/循环</t>
         </is>
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>格拉默冲锋</t>
+          <t>萤火回收</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>ATT_RAR_03</t>
+          <t>POW_UNC_11</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="D83" s="8" t="n">
@@ -8548,39 +9601,39 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>StarfireAnnihilation</t>
+          <t>ArmorBreaker</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>星火湮灭</t>
+          <t>破甲专家</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>[萤火]造成25点伤害。激发：造成50点伤害，施加5层灼热，费用1。升级：造成33/66点伤害。</t>
+          <t>你造成的伤害对格挡额外造成50%伤害。升级：额外造成100%伤害。</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>萤火/爆发</t>
+          <t>裂解/破甲</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>萤火终结技</t>
+          <t>裂解体系</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>ATT_RAR_04</t>
+          <t>POW_RAR_04</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -8589,43 +9642,43 @@
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>OmegaBlaster</t>
+          <t>ThreeDeaths</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>欧米伽爆破</t>
+          <t>三次死亡</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>消耗。对所有敌人造成20点伤害。施加5层灼热。升级：造成28点伤害，施加7层灼热。</t>
+          <t>本场战斗限3次：当你生命值降至1时，获得无敌1回合并抽2张牌。升级：获得无敌2回合。</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>灼热/AOE</t>
+          <t>生存/复活</t>
         </is>
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>消耗牌</t>
+          <t>流萤命运</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>ATT_RAR_05</t>
+          <t>POW_RAR_05</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
@@ -8634,43 +9687,43 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>FatalTrigger</t>
+          <t>FireflyNest</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>致命触发</t>
+          <t>萤火之巢</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>造成4点伤害。如果目标生命值低于25%，伤害变为3倍。升级：伤害变为4倍。</t>
+          <t>回合结束时，将手牌中一张随机非萤火牌变为萤火牌。升级：变2张。</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>收割</t>
+          <t>萤火/转化</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>斩杀</t>
+          <t>萤火生成</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>ATT_RAR_06</t>
+          <t>POW_RAR_06</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -8679,43 +9732,43 @@
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>DissolutionAnnihilation</t>
+          <t>Inferno</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>裂解湮灭</t>
+          <t>地狱火</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>对所有拥有裂解的敌人造成15点伤害。每有一个裂解敌人，获得3点格挡。升级：造成21点伤害。</t>
+          <t>灼热触发时，有50%概率不减少层数。升级：75%概率。</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>裂解/AOE</t>
+          <t>灼热/持续</t>
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>裂解收割</t>
+          <t>灼热增强</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>ATT_RAR_07</t>
+          <t>POW_RAR_07</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
@@ -8724,48 +9777,48 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>LastLight</t>
+          <t>EntropyMaster</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>最后之光</t>
+          <t>熵之主宰</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>生命值低于10点时才能打出。对所有敌人造成等于当前生命值的伤害。升级：伤害+10。</t>
+          <t>每当你赋予裂解，获得1点能量。升级：获得2点能量。</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>绝境/爆发</t>
+          <t>裂解/能量</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>萤火虫最后光芒</t>
+          <t>裂解体系</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>SKI_COM_05</t>
+          <t>POW_RAR_08</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
@@ -8773,44 +9826,44 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>EnergyBoost</t>
+          <t>LastStand</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>能量激增</t>
+          <t>背水一战</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>获得1点能量。抽1张牌。升级：获得2点能量。</t>
+          <t>生命值低于20点时，攻击牌耗能-1。升级：生命值低于25点时生效。</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>能量/过牌</t>
+          <t>自伤/减费</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>快速充能</t>
+          <t>低血量增益</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>SKI_COM_06</t>
+          <t>POW_RAR_09</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D89" s="8" t="n">
@@ -8818,89 +9871,89 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>ReinforcedArmor</t>
+          <t>FireflyBlessing</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>强化装甲</t>
+          <t>萤火祝福</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>获得12点格挡。如果你的生命值低于50%，额外获得6点格挡。升级：获得16点格挡。</t>
+          <t>萤火牌激发时效果额外+50%。升级：效果+100%。</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>格挡/生存</t>
+          <t>萤火/增强</t>
         </is>
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>SAM装甲</t>
+          <t>萤火核心</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>SKI_COM_07</t>
+          <t>POW_RAR_10</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>DesperateDefense</t>
+          <t>PhoenixRise</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>绝境防御</t>
+          <t>凤凰涅槃</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>获得5点格挡。生命值每低于最大值10点，格挡+2。升级：格挡+3。</t>
+          <t>本场战斗第一次死亡时，以50%生命值复活，激发所有手牌中的萤火牌。升级：以75%生命值复活。</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>格挡/生存</t>
+          <t>生存/复活</t>
         </is>
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>低血量加成</t>
+          <t>重生</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>SKI_COM_08</t>
+          <t>POW_RAR_11</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D91" s="8" t="n">
@@ -8908,1469 +9961,415 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>EmergencyRepair</t>
+          <t>ScorchAura</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>紧急修复</t>
+          <t>灼热光环</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>失去2点生命值。获得8点格挡。抽1张牌。升级：获得12点格挡。</t>
+          <t>回合开始时，对有灼热的敌人造成等同于灼热层数50%的伤害。升级：造成75%伤害。</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>自伤/格挡</t>
+          <t>灼热</t>
         </is>
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>快速修复</t>
+          <t>灼热增强</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>SKI_UNC_04</t>
+          <t>POW_RAR_12</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>FireflyDance</t>
+          <t>DissolutionCore</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>萤火之舞</t>
+          <t>裂解核心</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>抽2张牌。本回合你打出的下一张攻击牌费用为0。升级：抽3张牌。</t>
+          <t>裂解伤害翻倍。升级：裂解伤害×3。</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>过牌/减费</t>
+          <t>裂解</t>
         </is>
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>快速连击</t>
+          <t>裂解核心</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>SKI_UNC_05</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>ScorchAbsorb</t>
-        </is>
-      </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>灼热吸收</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>移除一个敌人身上的所有灼热。每移除1层，回复2点生命值。升级：回复3点生命值。</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>灼热/回复</t>
-        </is>
-      </c>
-      <c r="I93" s="8" t="inlineStr">
-        <is>
-          <t>灼热转化</t>
-        </is>
-      </c>
+      <c r="A93" s="8" t="n"/>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="8" t="n"/>
+      <c r="G93" s="8" t="n"/>
+      <c r="H93" s="8" t="n"/>
+      <c r="I93" s="8" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>SKI_UNC_06</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D94" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>BarrierTransfer</t>
-        </is>
-      </c>
-      <c r="F94" s="8" t="inlineStr">
-        <is>
-          <t>屏障转移</t>
-        </is>
-      </c>
-      <c r="G94" s="8" t="inlineStr">
-        <is>
-          <t>将目标敌人身上的所有格挡转移给自己。升级：转移的格挡+50%。</t>
-        </is>
-      </c>
-      <c r="H94" s="8" t="inlineStr">
-        <is>
-          <t>裂解/格挡</t>
-        </is>
-      </c>
-      <c r="I94" s="8" t="inlineStr">
-        <is>
-          <t>裂解体系</t>
-        </is>
-      </c>
+      <c r="A94" s="8" t="n"/>
+      <c r="B94" s="8" t="n"/>
+      <c r="C94" s="8" t="n"/>
+      <c r="D94" s="8" t="n"/>
+      <c r="E94" s="8" t="n"/>
+      <c r="F94" s="8" t="n"/>
+      <c r="G94" s="8" t="n"/>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="8" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>SKI_UNC_07</t>
-        </is>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D95" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t>FireflySpark</t>
-        </is>
-      </c>
-      <c r="F95" s="8" t="inlineStr">
-        <is>
-          <t>萤火迸发</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t>[萤火]激发手牌中一张萤火牌。升级：激发所有萤火牌。</t>
-        </is>
-      </c>
-      <c r="H95" s="8" t="inlineStr">
-        <is>
-          <t>萤火/激发</t>
-        </is>
-      </c>
-      <c r="I95" s="8" t="inlineStr">
-        <is>
-          <t>萤火辅助</t>
-        </is>
-      </c>
+      <c r="A95" s="8" t="n"/>
+      <c r="B95" s="8" t="n"/>
+      <c r="C95" s="8" t="n"/>
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="8" t="n"/>
+      <c r="F95" s="8" t="n"/>
+      <c r="G95" s="8" t="n"/>
+      <c r="H95" s="8" t="n"/>
+      <c r="I95" s="8" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>SKI_UNC_08</t>
-        </is>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D96" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t>TacticalRetreat</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>战术撤退</t>
-        </is>
-      </c>
-      <c r="G96" s="8" t="inlineStr">
-        <is>
-          <t>获得6点格挡。将手牌中所有萤火牌置入弃牌堆，每张抽1张牌。升级：获得9点格挡。</t>
-        </is>
-      </c>
-      <c r="H96" s="8" t="inlineStr">
-        <is>
-          <t>萤火/过牌</t>
-        </is>
-      </c>
-      <c r="I96" s="8" t="inlineStr">
-        <is>
-          <t>萤火循环</t>
-        </is>
-      </c>
+      <c r="A96" s="8" t="n"/>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="8" t="n"/>
+      <c r="D96" s="8" t="n"/>
+      <c r="E96" s="8" t="n"/>
+      <c r="F96" s="8" t="n"/>
+      <c r="G96" s="8" t="n"/>
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="8" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>SKI_UNC_09</t>
-        </is>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t>DissolutionField</t>
-        </is>
-      </c>
-      <c r="F97" s="8" t="inlineStr">
-        <is>
-          <t>裂解力场</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>对所有敌人赋予裂解。获得等于敌人数量×3的格挡。升级：获得×5的格挡。</t>
-        </is>
-      </c>
-      <c r="H97" s="8" t="inlineStr">
-        <is>
-          <t>裂解/防御</t>
-        </is>
-      </c>
-      <c r="I97" s="8" t="inlineStr">
-        <is>
-          <t>裂解体系</t>
-        </is>
-      </c>
+      <c r="A97" s="8" t="n"/>
+      <c r="B97" s="8" t="n"/>
+      <c r="C97" s="8" t="n"/>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="8" t="n"/>
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="8" t="n"/>
+      <c r="H97" s="8" t="n"/>
+      <c r="I97" s="8" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>SKI_UNC_10</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t>BurningSpirit</t>
-        </is>
-      </c>
-      <c r="F98" s="8" t="inlineStr">
-        <is>
-          <t>燃烧意志</t>
-        </is>
-      </c>
-      <c r="G98" s="8" t="inlineStr">
-        <is>
-          <t>失去4点生命值。本回合获得2层力量。升级：获得3层力量。</t>
-        </is>
-      </c>
-      <c r="H98" s="8" t="inlineStr">
-        <is>
-          <t>自伤/力量</t>
-        </is>
-      </c>
-      <c r="I98" s="8" t="inlineStr">
-        <is>
-          <t>燃烧增益</t>
-        </is>
-      </c>
+      <c r="A98" s="8" t="n"/>
+      <c r="B98" s="8" t="n"/>
+      <c r="C98" s="8" t="n"/>
+      <c r="D98" s="8" t="n"/>
+      <c r="E98" s="8" t="n"/>
+      <c r="F98" s="8" t="n"/>
+      <c r="G98" s="8" t="n"/>
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="8" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>SKI_UNC_11</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>EntropyShield</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>熵之盾</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>获得等于当前失去生命值一半的格挡。升级：获得等于失去生命值的格挡。</t>
-        </is>
-      </c>
-      <c r="H99" s="8" t="inlineStr">
-        <is>
-          <t>格挡/生存</t>
-        </is>
-      </c>
-      <c r="I99" s="8" t="inlineStr">
-        <is>
-          <t>低血量加成</t>
-        </is>
-      </c>
+      <c r="A99" s="8" t="n"/>
+      <c r="B99" s="8" t="n"/>
+      <c r="C99" s="8" t="n"/>
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="8" t="n"/>
+      <c r="F99" s="8" t="n"/>
+      <c r="G99" s="8" t="n"/>
+      <c r="H99" s="8" t="n"/>
+      <c r="I99" s="8" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t>SKI_UNC_12</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>QuickIgnition</t>
-        </is>
-      </c>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>快速点燃</t>
-        </is>
-      </c>
-      <c r="G100" s="8" t="inlineStr">
-        <is>
-          <t>选择手牌中一张牌，使其获得萤火属性。抽1张牌。升级：抽2张牌。</t>
-        </is>
-      </c>
-      <c r="H100" s="8" t="inlineStr">
-        <is>
-          <t>萤火/过牌</t>
-        </is>
-      </c>
-      <c r="I100" s="8" t="inlineStr">
-        <is>
-          <t>萤火赋予</t>
-        </is>
-      </c>
+      <c r="A100" s="8" t="n"/>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="8" t="n"/>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="8" t="n"/>
+      <c r="G100" s="8" t="n"/>
+      <c r="H100" s="8" t="n"/>
+      <c r="I100" s="8" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>SKI_RAR_04</t>
-        </is>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C101" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D101" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>LifeWhySleep</t>
-        </is>
-      </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>生命因何而沉睡</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>生命值上限减少10点。本场战斗获得3点能量。升级：减少8点，获得4点能量。</t>
-        </is>
-      </c>
-      <c r="H101" s="8" t="inlineStr">
-        <is>
-          <t>风险/能量</t>
-        </is>
-      </c>
-      <c r="I101" s="8" t="inlineStr">
-        <is>
-          <t>哲学命题</t>
-        </is>
-      </c>
+      <c r="A101" s="8" t="n"/>
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="8" t="n"/>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="8" t="n"/>
+      <c r="F101" s="8" t="n"/>
+      <c r="G101" s="8" t="n"/>
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="8" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
-        <is>
-          <t>SKI_RAR_05</t>
-        </is>
-      </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>FireflyCycle</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>萤火循环</t>
-        </is>
-      </c>
-      <c r="G102" s="8" t="inlineStr">
-        <is>
-          <t>将弃牌堆中所有萤火牌返回手牌。获得等于返回数量×2的格挡。升级：获得×3格挡。</t>
-        </is>
-      </c>
-      <c r="H102" s="8" t="inlineStr">
-        <is>
-          <t>萤火/循环</t>
-        </is>
-      </c>
-      <c r="I102" s="8" t="inlineStr">
-        <is>
-          <t>萤火回收</t>
-        </is>
-      </c>
+      <c r="A102" s="8" t="n"/>
+      <c r="B102" s="8" t="n"/>
+      <c r="C102" s="8" t="n"/>
+      <c r="D102" s="8" t="n"/>
+      <c r="E102" s="8" t="n"/>
+      <c r="F102" s="8" t="n"/>
+      <c r="G102" s="8" t="n"/>
+      <c r="H102" s="8" t="n"/>
+      <c r="I102" s="8" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="inlineStr">
-        <is>
-          <t>SKI_RAR_06</t>
-        </is>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D103" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>TimeStop</t>
-        </is>
-      </c>
-      <c r="F103" s="8" t="inlineStr">
-        <is>
-          <t>时停</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>本回合敌人不行动。你受到的所有伤害+5。消耗。升级：受到伤害+3。</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="inlineStr">
-        <is>
-          <t>控制/风险</t>
-        </is>
-      </c>
-      <c r="I103" s="8" t="inlineStr">
-        <is>
-          <t>时间停止</t>
-        </is>
-      </c>
+      <c r="A103" s="8" t="n"/>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="8" t="n"/>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="8" t="n"/>
+      <c r="F103" s="8" t="n"/>
+      <c r="G103" s="8" t="n"/>
+      <c r="H103" s="8" t="n"/>
+      <c r="I103" s="8" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t>SKI_RAR_07</t>
-        </is>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C104" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D104" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="8" t="inlineStr">
-        <is>
-          <t>OmeletCake</t>
-        </is>
-      </c>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t>橡木蛋糕卷</t>
-        </is>
-      </c>
-      <c r="G104" s="8" t="inlineStr">
-        <is>
-          <t>回复15点生命值。获得1点能量。每场战斗限用1次。升级：回复20点生命值，获得2点能量。</t>
-        </is>
-      </c>
-      <c r="H104" s="8" t="inlineStr">
-        <is>
-          <t>回复/能量</t>
-        </is>
-      </c>
-      <c r="I104" s="8" t="inlineStr">
-        <is>
-          <t>流萤最爱</t>
-        </is>
-      </c>
+      <c r="A104" s="8" t="n"/>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="8" t="n"/>
+      <c r="D104" s="8" t="n"/>
+      <c r="E104" s="8" t="n"/>
+      <c r="F104" s="8" t="n"/>
+      <c r="G104" s="8" t="n"/>
+      <c r="H104" s="8" t="n"/>
+      <c r="I104" s="8" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>SKI_RAR_08</t>
-        </is>
-      </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t>RooftopPhoto</t>
-        </is>
-      </c>
-      <c r="F105" s="8" t="inlineStr">
-        <is>
-          <t>天台合影</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr">
-        <is>
-          <t>获得8点格挡。抽1张牌。如果手牌中有萤火牌，额外获得4点格挡。升级：获得12点格挡，抽2张牌。</t>
-        </is>
-      </c>
-      <c r="H105" s="8" t="inlineStr">
-        <is>
-          <t>格挡/过牌</t>
-        </is>
-      </c>
-      <c r="I105" s="8" t="inlineStr">
-        <is>
-          <t>美好回忆</t>
-        </is>
-      </c>
+      <c r="A105" s="8" t="n"/>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="8" t="n"/>
+      <c r="D105" s="8" t="n"/>
+      <c r="E105" s="8" t="n"/>
+      <c r="F105" s="8" t="n"/>
+      <c r="G105" s="8" t="n"/>
+      <c r="H105" s="8" t="n"/>
+      <c r="I105" s="8" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>POW_UNC_03</t>
-        </is>
-      </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="8" t="inlineStr">
-        <is>
-          <t>ThermalReaction</t>
-        </is>
-      </c>
-      <c r="F106" s="8" t="inlineStr">
-        <is>
-          <t>热核反应</t>
-        </is>
-      </c>
-      <c r="G106" s="8" t="inlineStr">
-        <is>
-          <t>每当你施加灼热，获得1点格挡。升级：获得2点格挡。</t>
-        </is>
-      </c>
-      <c r="H106" s="8" t="inlineStr">
-        <is>
-          <t>灼热/格挡</t>
-        </is>
-      </c>
-      <c r="I106" s="8" t="inlineStr">
-        <is>
-          <t>灼热联动</t>
-        </is>
-      </c>
+      <c r="A106" s="8" t="n"/>
+      <c r="B106" s="8" t="n"/>
+      <c r="C106" s="8" t="n"/>
+      <c r="D106" s="8" t="n"/>
+      <c r="E106" s="8" t="n"/>
+      <c r="F106" s="8" t="n"/>
+      <c r="G106" s="8" t="n"/>
+      <c r="H106" s="8" t="n"/>
+      <c r="I106" s="8" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t>POW_UNC_04</t>
-        </is>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t>BurningWill</t>
-        </is>
-      </c>
-      <c r="F107" s="8" t="inlineStr">
-        <is>
-          <t>燃烧意志</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t>生命值低于50%时，伤害+2。升级：伤害+3。</t>
-        </is>
-      </c>
-      <c r="H107" s="8" t="inlineStr">
-        <is>
-          <t>自伤/力量</t>
-        </is>
-      </c>
-      <c r="I107" s="8" t="inlineStr">
-        <is>
-          <t>低血量增益</t>
-        </is>
-      </c>
+      <c r="A107" s="8" t="n"/>
+      <c r="B107" s="8" t="n"/>
+      <c r="C107" s="8" t="n"/>
+      <c r="D107" s="8" t="n"/>
+      <c r="E107" s="8" t="n"/>
+      <c r="F107" s="8" t="n"/>
+      <c r="G107" s="8" t="n"/>
+      <c r="H107" s="8" t="n"/>
+      <c r="I107" s="8" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>POW_UNC_05</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t>FireflyResonance</t>
-        </is>
-      </c>
-      <c r="F108" s="8" t="inlineStr">
-        <is>
-          <t>萤火共鸣</t>
-        </is>
-      </c>
-      <c r="G108" s="8" t="inlineStr">
-        <is>
-          <t>萤火牌激发时，额外获得1点能量。升级：获得2点能量。</t>
-        </is>
-      </c>
-      <c r="H108" s="8" t="inlineStr">
-        <is>
-          <t>萤火/能量</t>
-        </is>
-      </c>
-      <c r="I108" s="8" t="inlineStr">
-        <is>
-          <t>萤火增益</t>
-        </is>
-      </c>
+      <c r="A108" s="8" t="n"/>
+      <c r="B108" s="8" t="n"/>
+      <c r="C108" s="8" t="n"/>
+      <c r="D108" s="8" t="n"/>
+      <c r="E108" s="8" t="n"/>
+      <c r="F108" s="8" t="n"/>
+      <c r="G108" s="8" t="n"/>
+      <c r="H108" s="8" t="n"/>
+      <c r="I108" s="8" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>POW_UNC_06</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="8" t="inlineStr">
-        <is>
-          <t>BlockMastery</t>
-        </is>
-      </c>
-      <c r="F109" s="8" t="inlineStr">
-        <is>
-          <t>格挡精通</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
-        <is>
-          <t>从卡牌获得的格挡+3。升级：格挡+5。</t>
-        </is>
-      </c>
-      <c r="H109" s="8" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="I109" s="8" t="inlineStr">
-        <is>
-          <t>防御强化</t>
-        </is>
-      </c>
+      <c r="A109" s="8" t="n"/>
+      <c r="B109" s="8" t="n"/>
+      <c r="C109" s="8" t="n"/>
+      <c r="D109" s="8" t="n"/>
+      <c r="E109" s="8" t="n"/>
+      <c r="F109" s="8" t="n"/>
+      <c r="G109" s="8" t="n"/>
+      <c r="H109" s="8" t="n"/>
+      <c r="I109" s="8" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="inlineStr">
-        <is>
-          <t>POW_UNC_07</t>
-        </is>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t>ScorchMastery</t>
-        </is>
-      </c>
-      <c r="F110" s="8" t="inlineStr">
-        <is>
-          <t>灼热精通</t>
-        </is>
-      </c>
-      <c r="G110" s="8" t="inlineStr">
-        <is>
-          <t>施加的灼热层数+1。升级：灼热层数+2。</t>
-        </is>
-      </c>
-      <c r="H110" s="8" t="inlineStr">
-        <is>
-          <t>灼热</t>
-        </is>
-      </c>
-      <c r="I110" s="8" t="inlineStr">
-        <is>
-          <t>灼热强化</t>
-        </is>
-      </c>
+      <c r="A110" s="8" t="n"/>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="8" t="n"/>
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="8" t="n"/>
+      <c r="F110" s="8" t="n"/>
+      <c r="G110" s="8" t="n"/>
+      <c r="H110" s="8" t="n"/>
+      <c r="I110" s="8" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="inlineStr">
-        <is>
-          <t>POW_UNC_08</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C111" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t>DissolutionResonance</t>
-        </is>
-      </c>
-      <c r="F111" s="8" t="inlineStr">
-        <is>
-          <t>裂解共鸣</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t>触发裂解伤害时，额外造成等于伤害值20%的伤害。升级：30%额外伤害。</t>
-        </is>
-      </c>
-      <c r="H111" s="8" t="inlineStr">
-        <is>
-          <t>裂解</t>
-        </is>
-      </c>
-      <c r="I111" s="8" t="inlineStr">
-        <is>
-          <t>裂解强化</t>
-        </is>
-      </c>
+      <c r="A111" s="8" t="n"/>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="8" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="8" t="n"/>
+      <c r="F111" s="8" t="n"/>
+      <c r="G111" s="8" t="n"/>
+      <c r="H111" s="8" t="n"/>
+      <c r="I111" s="8" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t>POW_UNC_09</t>
-        </is>
-      </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t>LifeExchange</t>
-        </is>
-      </c>
-      <c r="F112" s="8" t="inlineStr">
-        <is>
-          <t>生命交换</t>
-        </is>
-      </c>
-      <c r="G112" s="8" t="inlineStr">
-        <is>
-          <t>回合开始时，失去2点生命值，获得1层力量。升级：失去1点生命值。</t>
-        </is>
-      </c>
-      <c r="H112" s="8" t="inlineStr">
-        <is>
-          <t>自伤/力量</t>
-        </is>
-      </c>
-      <c r="I112" s="8" t="inlineStr">
-        <is>
-          <t>生命转化</t>
-        </is>
-      </c>
+      <c r="A112" s="8" t="n"/>
+      <c r="B112" s="8" t="n"/>
+      <c r="C112" s="8" t="n"/>
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="8" t="n"/>
+      <c r="F112" s="8" t="n"/>
+      <c r="G112" s="8" t="n"/>
+      <c r="H112" s="8" t="n"/>
+      <c r="I112" s="8" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="8" t="inlineStr">
-        <is>
-          <t>POW_UNC_10</t>
-        </is>
-      </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t>FireflyMemory</t>
-        </is>
-      </c>
-      <c r="F113" s="8" t="inlineStr">
-        <is>
-          <t>萤火记忆</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>萤火牌被打出后，有50%概率返回手牌。升级：75%概率。</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="inlineStr">
-        <is>
-          <t>萤火/循环</t>
-        </is>
-      </c>
-      <c r="I113" s="8" t="inlineStr">
-        <is>
-          <t>萤火回收</t>
-        </is>
-      </c>
+      <c r="A113" s="8" t="n"/>
+      <c r="B113" s="8" t="n"/>
+      <c r="C113" s="8" t="n"/>
+      <c r="D113" s="8" t="n"/>
+      <c r="E113" s="8" t="n"/>
+      <c r="F113" s="8" t="n"/>
+      <c r="G113" s="8" t="n"/>
+      <c r="H113" s="8" t="n"/>
+      <c r="I113" s="8" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t>POW_UNC_11</t>
-        </is>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t>ArmorBreaker</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t>破甲专家</t>
-        </is>
-      </c>
-      <c r="G114" s="8" t="inlineStr">
-        <is>
-          <t>你造成的伤害对格挡额外造成50%伤害。升级：额外造成100%伤害。</t>
-        </is>
-      </c>
-      <c r="H114" s="8" t="inlineStr">
-        <is>
-          <t>裂解/破甲</t>
-        </is>
-      </c>
-      <c r="I114" s="8" t="inlineStr">
-        <is>
-          <t>裂解体系</t>
-        </is>
-      </c>
+      <c r="A114" s="8" t="n"/>
+      <c r="B114" s="8" t="n"/>
+      <c r="C114" s="8" t="n"/>
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="8" t="n"/>
+      <c r="F114" s="8" t="n"/>
+      <c r="G114" s="8" t="n"/>
+      <c r="H114" s="8" t="n"/>
+      <c r="I114" s="8" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="inlineStr">
-        <is>
-          <t>POW_RAR_04</t>
-        </is>
-      </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E115" s="8" t="inlineStr">
-        <is>
-          <t>ThreeDeaths</t>
-        </is>
-      </c>
-      <c r="F115" s="8" t="inlineStr">
-        <is>
-          <t>三次死亡</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr">
-        <is>
-          <t>本场战斗限3次：当你生命值降至1时，获得无敌1回合并抽2张牌。升级：获得无敌2回合。</t>
-        </is>
-      </c>
-      <c r="H115" s="8" t="inlineStr">
-        <is>
-          <t>生存/复活</t>
-        </is>
-      </c>
-      <c r="I115" s="8" t="inlineStr">
-        <is>
-          <t>流萤命运</t>
-        </is>
-      </c>
+      <c r="A115" s="8" t="n"/>
+      <c r="B115" s="8" t="n"/>
+      <c r="C115" s="8" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="8" t="n"/>
+      <c r="F115" s="8" t="n"/>
+      <c r="G115" s="8" t="n"/>
+      <c r="H115" s="8" t="n"/>
+      <c r="I115" s="8" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t>POW_RAR_05</t>
-        </is>
-      </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t>FireflyNest</t>
-        </is>
-      </c>
-      <c r="F116" s="8" t="inlineStr">
-        <is>
-          <t>萤火之巢</t>
-        </is>
-      </c>
-      <c r="G116" s="8" t="inlineStr">
-        <is>
-          <t>回合结束时，将手牌中一张随机非萤火牌变为萤火牌。升级：变2张。</t>
-        </is>
-      </c>
-      <c r="H116" s="8" t="inlineStr">
-        <is>
-          <t>萤火/转化</t>
-        </is>
-      </c>
-      <c r="I116" s="8" t="inlineStr">
-        <is>
-          <t>萤火生成</t>
-        </is>
-      </c>
+      <c r="A116" s="8" t="n"/>
+      <c r="B116" s="8" t="n"/>
+      <c r="C116" s="8" t="n"/>
+      <c r="D116" s="8" t="n"/>
+      <c r="E116" s="8" t="n"/>
+      <c r="F116" s="8" t="n"/>
+      <c r="G116" s="8" t="n"/>
+      <c r="H116" s="8" t="n"/>
+      <c r="I116" s="8" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t>POW_RAR_06</t>
-        </is>
-      </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t>Inferno</t>
-        </is>
-      </c>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>地狱火</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>灼热触发时，有50%概率不减少层数。升级：75%概率。</t>
-        </is>
-      </c>
-      <c r="H117" s="8" t="inlineStr">
-        <is>
-          <t>灼热/持续</t>
-        </is>
-      </c>
-      <c r="I117" s="8" t="inlineStr">
-        <is>
-          <t>灼热增强</t>
-        </is>
-      </c>
+      <c r="A117" s="8" t="n"/>
+      <c r="B117" s="8" t="n"/>
+      <c r="C117" s="8" t="n"/>
+      <c r="D117" s="8" t="n"/>
+      <c r="E117" s="8" t="n"/>
+      <c r="F117" s="8" t="n"/>
+      <c r="G117" s="8" t="n"/>
+      <c r="H117" s="8" t="n"/>
+      <c r="I117" s="8" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t>POW_RAR_07</t>
-        </is>
-      </c>
-      <c r="B118" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t>EntropyMaster</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="inlineStr">
-        <is>
-          <t>熵之主宰</t>
-        </is>
-      </c>
-      <c r="G118" s="8" t="inlineStr">
-        <is>
-          <t>每当你赋予裂解，获得1点能量。升级：获得2点能量。</t>
-        </is>
-      </c>
-      <c r="H118" s="8" t="inlineStr">
-        <is>
-          <t>裂解/能量</t>
-        </is>
-      </c>
-      <c r="I118" s="8" t="inlineStr">
-        <is>
-          <t>裂解体系</t>
-        </is>
-      </c>
+      <c r="A118" s="8" t="n"/>
+      <c r="B118" s="8" t="n"/>
+      <c r="C118" s="8" t="n"/>
+      <c r="D118" s="8" t="n"/>
+      <c r="E118" s="8" t="n"/>
+      <c r="F118" s="8" t="n"/>
+      <c r="G118" s="8" t="n"/>
+      <c r="H118" s="8" t="n"/>
+      <c r="I118" s="8" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="inlineStr">
-        <is>
-          <t>POW_RAR_08</t>
-        </is>
-      </c>
-      <c r="B119" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t>LastStand</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="inlineStr">
-        <is>
-          <t>背水一战</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr">
-        <is>
-          <t>生命值低于20点时，攻击牌耗能-1。升级：生命值低于25点时生效。</t>
-        </is>
-      </c>
-      <c r="H119" s="8" t="inlineStr">
-        <is>
-          <t>自伤/减费</t>
-        </is>
-      </c>
-      <c r="I119" s="8" t="inlineStr">
-        <is>
-          <t>低血量增益</t>
-        </is>
-      </c>
+      <c r="A119" s="8" t="n"/>
+      <c r="B119" s="8" t="n"/>
+      <c r="C119" s="8" t="n"/>
+      <c r="D119" s="8" t="n"/>
+      <c r="E119" s="8" t="n"/>
+      <c r="F119" s="8" t="n"/>
+      <c r="G119" s="8" t="n"/>
+      <c r="H119" s="8" t="n"/>
+      <c r="I119" s="8" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t>POW_RAR_09</t>
-        </is>
-      </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t>FireflyBlessing</t>
-        </is>
-      </c>
-      <c r="F120" s="8" t="inlineStr">
-        <is>
-          <t>萤火祝福</t>
-        </is>
-      </c>
-      <c r="G120" s="8" t="inlineStr">
-        <is>
-          <t>萤火牌激发时效果额外+50%。升级：效果+100%。</t>
-        </is>
-      </c>
-      <c r="H120" s="8" t="inlineStr">
-        <is>
-          <t>萤火/增强</t>
-        </is>
-      </c>
-      <c r="I120" s="8" t="inlineStr">
-        <is>
-          <t>萤火核心</t>
-        </is>
-      </c>
+      <c r="A120" s="8" t="n"/>
+      <c r="B120" s="8" t="n"/>
+      <c r="C120" s="8" t="n"/>
+      <c r="D120" s="8" t="n"/>
+      <c r="E120" s="8" t="n"/>
+      <c r="F120" s="8" t="n"/>
+      <c r="G120" s="8" t="n"/>
+      <c r="H120" s="8" t="n"/>
+      <c r="I120" s="8" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t>POW_RAR_10</t>
-        </is>
-      </c>
-      <c r="B121" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C121" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D121" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t>PhoenixRise</t>
-        </is>
-      </c>
-      <c r="F121" s="8" t="inlineStr">
-        <is>
-          <t>凤凰涅槃</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr">
-        <is>
-          <t>本场战斗第一次死亡时，以50%生命值复活，激发所有手牌中的萤火牌。升级：以75%生命值复活。</t>
-        </is>
-      </c>
-      <c r="H121" s="8" t="inlineStr">
-        <is>
-          <t>生存/复活</t>
-        </is>
-      </c>
-      <c r="I121" s="8" t="inlineStr">
-        <is>
-          <t>重生</t>
-        </is>
-      </c>
+      <c r="A121" s="8" t="n"/>
+      <c r="B121" s="8" t="n"/>
+      <c r="C121" s="8" t="n"/>
+      <c r="D121" s="8" t="n"/>
+      <c r="E121" s="8" t="n"/>
+      <c r="F121" s="8" t="n"/>
+      <c r="G121" s="8" t="n"/>
+      <c r="H121" s="8" t="n"/>
+      <c r="I121" s="8" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t>POW_RAR_11</t>
-        </is>
-      </c>
-      <c r="B122" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D122" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t>ScorchAura</t>
-        </is>
-      </c>
-      <c r="F122" s="8" t="inlineStr">
-        <is>
-          <t>灼热光环</t>
-        </is>
-      </c>
-      <c r="G122" s="8" t="inlineStr">
-        <is>
-          <t>回合开始时，对有灼热的敌人造成等同于灼热层数50%的伤害。升级：造成75%伤害。</t>
-        </is>
-      </c>
-      <c r="H122" s="8" t="inlineStr">
-        <is>
-          <t>灼热</t>
-        </is>
-      </c>
-      <c r="I122" s="8" t="inlineStr">
-        <is>
-          <t>灼热增强</t>
-        </is>
-      </c>
+      <c r="A122" s="8" t="n"/>
+      <c r="B122" s="8" t="n"/>
+      <c r="C122" s="8" t="n"/>
+      <c r="D122" s="8" t="n"/>
+      <c r="E122" s="8" t="n"/>
+      <c r="F122" s="8" t="n"/>
+      <c r="G122" s="8" t="n"/>
+      <c r="H122" s="8" t="n"/>
+      <c r="I122" s="8" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>POW_RAR_12</t>
-        </is>
-      </c>
-      <c r="B123" s="8" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t>DissolutionCore</t>
-        </is>
-      </c>
-      <c r="F123" s="8" t="inlineStr">
-        <is>
-          <t>裂解核心</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr">
-        <is>
-          <t>裂解伤害翻倍。升级：裂解伤害×3。</t>
-        </is>
-      </c>
-      <c r="H123" s="8" t="inlineStr">
-        <is>
-          <t>裂解</t>
-        </is>
-      </c>
-      <c r="I123" s="8" t="inlineStr">
-        <is>
-          <t>裂解核心</t>
-        </is>
-      </c>
+      <c r="A123" s="8" t="n"/>
+      <c r="B123" s="8" t="n"/>
+      <c r="C123" s="8" t="n"/>
+      <c r="D123" s="8" t="n"/>
+      <c r="E123" s="8" t="n"/>
+      <c r="F123" s="8" t="n"/>
+      <c r="G123" s="8" t="n"/>
+      <c r="H123" s="8" t="n"/>
+      <c r="I123" s="8" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/docs/firefly_card_benchmark_template.xlsx
+++ b/docs/firefly_card_benchmark_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\personal\game_t\firefly\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C5A9C9-4777-48DD-B245-F3785BE08AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44FC669-E7AE-4CC3-80A9-6C069139355A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1728,9 +1728,6 @@
     <t>GrappleStrike</t>
   </si>
   <si>
-    <t>擒拿斩</t>
-  </si>
-  <si>
     <t>造成8点伤害。如果本回合造成过伤害，伤害+4。升级：伤害+6。</t>
   </si>
   <si>
@@ -1749,9 +1746,6 @@
     <t>迅捷斩</t>
   </si>
   <si>
-    <t>造成4点伤害。抽1张牌。升级：造成7点伤害。</t>
-  </si>
-  <si>
     <t>过牌</t>
   </si>
   <si>
@@ -1785,9 +1779,6 @@
     <t>熵减宿命</t>
   </si>
   <si>
-    <t>对所有敌人造成6点伤害。对所有有格挡的敌人赋予裂解。升级：造成9点伤害。</t>
-  </si>
-  <si>
     <t>裂解/AOE</t>
   </si>
   <si>
@@ -1848,9 +1839,6 @@
     <t>PrecisionStrike</t>
   </si>
   <si>
-    <t>精准打击</t>
-  </si>
-  <si>
     <t>造成9点伤害。如果目标有裂解，抽1张牌。升级：抽2张牌。</t>
   </si>
   <si>
@@ -1944,9 +1932,6 @@
     <t>莽撞冲锋</t>
   </si>
   <si>
-    <t>失去3点生命值。造成10点伤害。如果目标死于这张牌，回复3点生命值。升级：造成14点伤害。</t>
-  </si>
-  <si>
     <t>自伤</t>
   </si>
   <si>
@@ -1992,12 +1977,6 @@
     <t>FatalTrigger</t>
   </si>
   <si>
-    <t>致命触发</t>
-  </si>
-  <si>
-    <t>造成10点伤害。如果目标生命值低于25%，伤害变为3倍。升级：伤害变为4倍。</t>
-  </si>
-  <si>
     <t>收割</t>
   </si>
   <si>
@@ -2010,12 +1989,6 @@
     <t>DissolutionAnnihilation</t>
   </si>
   <si>
-    <t>裂解湮灭</t>
-  </si>
-  <si>
-    <t>对所有拥有裂解的敌人造成15点伤害。每有一个裂解敌人，获得3点格挡。升级：造成21点伤害。</t>
-  </si>
-  <si>
     <t>裂解收割</t>
   </si>
   <si>
@@ -2025,12 +1998,6 @@
     <t>LastLight</t>
   </si>
   <si>
-    <t>最后之光</t>
-  </si>
-  <si>
-    <t>生命值低于10点时才能打出。对所有敌人造成等于当前生命值的伤害。升级：伤害+10。</t>
-  </si>
-  <si>
     <t>绝境/爆发</t>
   </si>
   <si>
@@ -2043,9 +2010,6 @@
     <t>EnergyBoost</t>
   </si>
   <si>
-    <t>盛宴花火</t>
-  </si>
-  <si>
     <t>获得1点能量。抽1张牌。升级：获得2点能量。</t>
   </si>
   <si>
@@ -2073,9 +2037,6 @@
     <t>DesperateDefense</t>
   </si>
   <si>
-    <t>绝境防御</t>
-  </si>
-  <si>
     <t>低血量加成</t>
   </si>
   <si>
@@ -2134,9 +2095,6 @@
   </si>
   <si>
     <t>BarrierTransfer</t>
-  </si>
-  <si>
-    <t>屏障转移</t>
   </si>
   <si>
     <t>将目标敌人身上的所有格挡转移给自己。升级：转移的格挡+50%。</t>
@@ -2685,6 +2643,62 @@
   </si>
   <si>
     <t>对所有拥有裂解的敌人，无视格挡造成等同于其裂解源层数的伤害。升级：2费。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成4点伤害。抽1张牌。升级：造成7点伤害。抽两张牌</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲锋</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>给予所有敌人6层格挡。对所有有格挡的敌人赋予裂解。升级：给予9层格挡。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>失去5点生命值。造成20点伤害。如果目标死于这张牌，回复7点生命值。升级：造成25点伤害。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值低于10点时才能打出。对所有敌人造成等于已失去生命值的伤害。升级：低于20点时才能打出</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>静默的星河</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞萤之火</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤染之茧</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成15点伤害。如果目标生命值低于25%，伤害变为3倍。升级：伤害变为4倍。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>对所有拥有裂解的敌人造成15点伤害。每有一个裂解敌人，获得3点格挡。升级：造成21点伤害。获得5层格挡</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>晖长石的烟火</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>从梦中醒来</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜色名为温柔</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>何物朝向死亡</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -6774,7 +6788,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>423</v>
@@ -6792,7 +6806,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>847</v>
+        <v>833</v>
       </c>
       <c r="D3" s="5">
         <v>1</v>
@@ -6804,7 +6818,7 @@
         <v>426</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>838</v>
+        <v>824</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>427</v>
@@ -6828,10 +6842,10 @@
         <v>75</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>841</v>
+        <v>827</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>429</v>
@@ -6940,10 +6954,10 @@
         <v>26</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>839</v>
+        <v>825</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>840</v>
+        <v>826</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>441</v>
@@ -6967,7 +6981,7 @@
         <v>32</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>443</v>
@@ -7053,7 +7067,7 @@
         <v>455</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>843</v>
+        <v>829</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>456</v>
@@ -7107,7 +7121,7 @@
         <v>136</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>856</v>
+        <v>842</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>461</v>
@@ -7133,7 +7147,7 @@
         <v>19</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>828</v>
+        <v>814</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>463</v>
@@ -7189,7 +7203,7 @@
         <v>51</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>848</v>
+        <v>834</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>470</v>
@@ -7245,10 +7259,10 @@
         <v>104</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>852</v>
+        <v>838</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>830</v>
+        <v>816</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>476</v>
@@ -7272,10 +7286,10 @@
         <v>80</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>853</v>
+        <v>839</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>836</v>
+        <v>822</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>478</v>
@@ -7299,7 +7313,7 @@
         <v>55</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>849</v>
+        <v>835</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>480</v>
@@ -7355,10 +7369,10 @@
         <v>487</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>846</v>
+        <v>832</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>488</v>
@@ -7373,7 +7387,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="D24" s="5">
         <v>2</v>
@@ -7443,7 +7457,7 @@
         <v>497</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>851</v>
+        <v>837</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>498</v>
@@ -7526,7 +7540,7 @@
         <v>511</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>854</v>
+        <v>840</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>512</v>
@@ -7553,7 +7567,7 @@
         <v>515</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>855</v>
+        <v>841</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>516</v>
@@ -7650,7 +7664,7 @@
         <v>529</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>48</v>
@@ -7679,7 +7693,7 @@
         <v>535</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>48</v>
@@ -7749,21 +7763,21 @@
         <v>546</v>
       </c>
       <c r="F37" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="H37" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="I37" s="5" t="s">
         <v>549</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>12</v>
@@ -7775,24 +7789,24 @@
         <v>0</v>
       </c>
       <c r="E38" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="G38" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="I38" s="5" t="s">
         <v>554</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>12</v>
@@ -7804,24 +7818,24 @@
         <v>1</v>
       </c>
       <c r="E39" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="G39" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="H39" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="I39" s="5" t="s">
         <v>560</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>12</v>
@@ -7833,16 +7847,16 @@
         <v>2</v>
       </c>
       <c r="E40" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>564</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>567</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>436</v>
@@ -7850,7 +7864,7 @@
     </row>
     <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="4" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>12</v>
@@ -7862,24 +7876,24 @@
         <v>3</v>
       </c>
       <c r="E41" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="H41" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="I41" s="5" t="s">
         <v>570</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>12</v>
@@ -7891,24 +7905,24 @@
         <v>1</v>
       </c>
       <c r="E42" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="H42" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="I42" s="5" t="s">
         <v>576</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>577</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="4" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>12</v>
@@ -7920,24 +7934,24 @@
         <v>2</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>494</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="4" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>12</v>
@@ -7949,24 +7963,24 @@
         <v>1</v>
       </c>
       <c r="E44" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="I44" s="5" t="s">
         <v>586</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="4" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>12</v>
@@ -7978,16 +7992,16 @@
         <v>2</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>436</v>
@@ -7995,7 +8009,7 @@
     </row>
     <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="4" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>12</v>
@@ -8007,24 +8021,24 @@
         <v>0</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>837</v>
+        <v>823</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>427</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="4" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>12</v>
@@ -8036,24 +8050,24 @@
         <v>2</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>498</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="4" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>12</v>
@@ -8065,16 +8079,16 @@
         <v>1</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="I48" s="5" t="s">
         <v>436</v>
@@ -8082,7 +8096,7 @@
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="4" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>12</v>
@@ -8094,24 +8108,24 @@
         <v>2</v>
       </c>
       <c r="E49" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="I49" s="5" t="s">
         <v>611</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>612</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="4" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>12</v>
@@ -8123,24 +8137,24 @@
         <v>1</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>619</v>
+        <v>846</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>12</v>
@@ -8152,24 +8166,24 @@
         <v>2</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>12</v>
@@ -8181,24 +8195,24 @@
         <v>3</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>498</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>12</v>
@@ -8210,24 +8224,24 @@
         <v>1</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>635</v>
+        <v>856</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>636</v>
+        <v>851</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="4" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>12</v>
@@ -8239,24 +8253,24 @@
         <v>2</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>641</v>
+        <v>848</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>642</v>
+        <v>852</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="4" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>12</v>
@@ -8268,24 +8282,24 @@
         <v>0</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>646</v>
+        <v>849</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>647</v>
+        <v>847</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="4" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>21</v>
@@ -8297,24 +8311,24 @@
         <v>1</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>652</v>
+        <v>853</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="4" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>21</v>
@@ -8326,24 +8340,24 @@
         <v>1</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>835</v>
+        <v>821</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>834</v>
+        <v>820</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="4" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>21</v>
@@ -8355,24 +8369,24 @@
         <v>0</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>662</v>
+        <v>850</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>833</v>
+        <v>819</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="4" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>21</v>
@@ -8384,24 +8398,24 @@
         <v>1</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="4" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>21</v>
@@ -8413,24 +8427,24 @@
         <v>1</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="4" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>21</v>
@@ -8442,24 +8456,24 @@
         <v>1</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>831</v>
+        <v>817</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="4" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>21</v>
@@ -8471,16 +8485,16 @@
         <v>2</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>683</v>
+        <v>854</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>436</v>
@@ -8488,7 +8502,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="B63" t="s">
         <v>21</v>
@@ -8500,24 +8514,24 @@
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="F63" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="G63" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="H63" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="I63" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="B64" t="s">
         <v>21</v>
@@ -8529,13 +8543,13 @@
         <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="F64" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="G64" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="H64" t="s">
         <v>474</v>
@@ -8546,7 +8560,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="B65" t="s">
         <v>21</v>
@@ -8558,24 +8572,24 @@
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="F65" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="G65" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="H65" t="s">
         <v>508</v>
       </c>
       <c r="I65" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="B66" t="s">
         <v>21</v>
@@ -8587,24 +8601,24 @@
         <v>2</v>
       </c>
       <c r="E66" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="F66" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="G66" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="H66" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="I66" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="B67" t="s">
         <v>21</v>
@@ -8616,24 +8630,24 @@
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="F67" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="G67" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="H67" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="I67" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="B68" t="s">
         <v>21</v>
@@ -8645,24 +8659,24 @@
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="F68" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="G68" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="H68" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="I68" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="B69" t="s">
         <v>21</v>
@@ -8674,24 +8688,24 @@
         <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="F69" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="G69" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H69" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="I69" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="B70" t="s">
         <v>21</v>
@@ -8703,24 +8717,24 @@
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="F70" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="G70" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="H70" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="I70" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="B71" t="s">
         <v>21</v>
@@ -8732,24 +8746,24 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="F71" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="G71" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="H71" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="I71" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="B72" t="s">
         <v>21</v>
@@ -8761,24 +8775,24 @@
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="F72" t="s">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="G72" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="H72" t="s">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="I72" t="s">
-        <v>736</v>
+        <v>722</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>737</v>
+        <v>723</v>
       </c>
       <c r="B73" t="s">
         <v>41</v>
@@ -8790,24 +8804,24 @@
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>738</v>
+        <v>724</v>
       </c>
       <c r="F73" t="s">
-        <v>739</v>
+        <v>725</v>
       </c>
       <c r="G73" t="s">
-        <v>740</v>
+        <v>726</v>
       </c>
       <c r="H73" t="s">
-        <v>741</v>
+        <v>727</v>
       </c>
       <c r="I73" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="B74" t="s">
         <v>41</v>
@@ -8819,24 +8833,24 @@
         <v>2</v>
       </c>
       <c r="E74" t="s">
-        <v>743</v>
+        <v>729</v>
       </c>
       <c r="F74" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="G74" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="H74" t="s">
         <v>508</v>
       </c>
       <c r="I74" t="s">
-        <v>745</v>
+        <v>731</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="B75" t="s">
         <v>41</v>
@@ -8848,24 +8862,24 @@
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="F75" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
       <c r="G75" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
       <c r="H75" t="s">
         <v>488</v>
       </c>
       <c r="I75" t="s">
-        <v>750</v>
+        <v>736</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>751</v>
+        <v>737</v>
       </c>
       <c r="B76" t="s">
         <v>41</v>
@@ -8877,24 +8891,24 @@
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>752</v>
+        <v>738</v>
       </c>
       <c r="F76" t="s">
-        <v>753</v>
+        <v>739</v>
       </c>
       <c r="G76" t="s">
-        <v>754</v>
+        <v>740</v>
       </c>
       <c r="H76" t="s">
-        <v>755</v>
+        <v>741</v>
       </c>
       <c r="I76" t="s">
-        <v>756</v>
+        <v>742</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="B77" t="s">
         <v>41</v>
@@ -8906,24 +8920,24 @@
         <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>758</v>
+        <v>744</v>
       </c>
       <c r="F77" t="s">
-        <v>759</v>
+        <v>745</v>
       </c>
       <c r="G77" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="H77" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I77" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
       <c r="B78" t="s">
         <v>41</v>
@@ -8935,24 +8949,24 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="F78" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="G78" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="H78" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="I78" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
       <c r="B79" t="s">
         <v>41</v>
@@ -8964,24 +8978,24 @@
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
       <c r="F79" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
       <c r="G79" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="H79" t="s">
         <v>508</v>
       </c>
       <c r="I79" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>772</v>
+        <v>758</v>
       </c>
       <c r="B80" t="s">
         <v>41</v>
@@ -8993,24 +9007,24 @@
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>773</v>
+        <v>759</v>
       </c>
       <c r="F80" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="G80" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="H80" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="I80" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="B81" t="s">
         <v>41</v>
@@ -9022,16 +9036,16 @@
         <v>2</v>
       </c>
       <c r="E81" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="F81" t="s">
-        <v>778</v>
+        <v>764</v>
       </c>
       <c r="G81" t="s">
-        <v>779</v>
+        <v>765</v>
       </c>
       <c r="H81" t="s">
-        <v>780</v>
+        <v>766</v>
       </c>
       <c r="I81" t="s">
         <v>436</v>
@@ -9039,7 +9053,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>781</v>
+        <v>767</v>
       </c>
       <c r="B82" t="s">
         <v>41</v>
@@ -9051,24 +9065,24 @@
         <v>2</v>
       </c>
       <c r="E82" t="s">
-        <v>782</v>
+        <v>768</v>
       </c>
       <c r="F82" t="s">
-        <v>783</v>
+        <v>769</v>
       </c>
       <c r="G82" t="s">
-        <v>784</v>
+        <v>770</v>
       </c>
       <c r="H82" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="I82" t="s">
-        <v>786</v>
+        <v>772</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="B83" t="s">
         <v>41</v>
@@ -9080,24 +9094,24 @@
         <v>2</v>
       </c>
       <c r="E83" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
       <c r="F83" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="G83" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="H83" t="s">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="I83" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="B84" t="s">
         <v>41</v>
@@ -9112,21 +9126,21 @@
         <v>291</v>
       </c>
       <c r="F84" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="G84" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="H84" t="s">
         <v>528</v>
       </c>
       <c r="I84" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
       <c r="B85" t="s">
         <v>41</v>
@@ -9138,16 +9152,16 @@
         <v>2</v>
       </c>
       <c r="E85" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="F85" t="s">
-        <v>799</v>
+        <v>785</v>
       </c>
       <c r="G85" t="s">
-        <v>800</v>
+        <v>786</v>
       </c>
       <c r="H85" t="s">
-        <v>801</v>
+        <v>787</v>
       </c>
       <c r="I85" t="s">
         <v>436</v>
@@ -9155,7 +9169,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>802</v>
+        <v>788</v>
       </c>
       <c r="B86" t="s">
         <v>41</v>
@@ -9167,24 +9181,24 @@
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="F86" t="s">
-        <v>804</v>
+        <v>790</v>
       </c>
       <c r="G86" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="H86" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="I86" t="s">
-        <v>745</v>
+        <v>731</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="B87" t="s">
         <v>41</v>
@@ -9196,24 +9210,24 @@
         <v>2</v>
       </c>
       <c r="E87" t="s">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="F87" t="s">
-        <v>809</v>
+        <v>795</v>
       </c>
       <c r="G87" t="s">
-        <v>810</v>
+        <v>796</v>
       </c>
       <c r="H87" t="s">
-        <v>811</v>
+        <v>797</v>
       </c>
       <c r="I87" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>813</v>
+        <v>799</v>
       </c>
       <c r="B88" t="s">
         <v>41</v>
@@ -9225,19 +9239,19 @@
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>814</v>
+        <v>800</v>
       </c>
       <c r="F88" t="s">
-        <v>815</v>
+        <v>801</v>
       </c>
       <c r="G88" t="s">
-        <v>816</v>
+        <v>802</v>
       </c>
       <c r="H88" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I88" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
     </row>
   </sheetData>
@@ -9258,42 +9272,42 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
-        <v>817</v>
+        <v>803</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>818</v>
+        <v>804</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
-        <v>819</v>
+        <v>805</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>820</v>
+        <v>806</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
-        <v>821</v>
+        <v>807</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>822</v>
+        <v>808</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
-        <v>823</v>
+        <v>809</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>826</v>
+        <v>812</v>
       </c>
     </row>
   </sheetData>

--- a/docs/firefly_card_benchmark_template.xlsx
+++ b/docs/firefly_card_benchmark_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\personal\game_t\firefly\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44FC669-E7AE-4CC3-80A9-6C069139355A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAAD6E14-0AC4-4A65-8931-F898ED014A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="854">
   <si>
     <t>序号</t>
   </si>
@@ -1557,18 +1557,12 @@
     <t>SKI_RAR_01</t>
   </si>
   <si>
-    <t>激发手牌中所有萤火牌。升级：费用1。</t>
-  </si>
-  <si>
     <t>我将点燃大海</t>
   </si>
   <si>
     <t>SKI_RAR_02</t>
   </si>
   <si>
-    <t>打出手牌中所有的萤火牌。升级：费用1。</t>
-  </si>
-  <si>
     <t>萤火/连击</t>
   </si>
   <si>
@@ -2082,9 +2076,6 @@
     <t>ScorchAbsorb</t>
   </si>
   <si>
-    <t>灼热吸收</t>
-  </si>
-  <si>
     <t>灼热/回复</t>
   </si>
   <si>
@@ -2106,9 +2097,6 @@
     <t>TacticalRetreat</t>
   </si>
   <si>
-    <t>战术撤退</t>
-  </si>
-  <si>
     <t>获得6点格挡。将手牌中所有萤火牌置入弃牌堆，每张抽1张牌。升级：获得9点格挡。</t>
   </si>
   <si>
@@ -2118,18 +2106,6 @@
     <t>萤火循环</t>
   </si>
   <si>
-    <t>SKI_UNC_09</t>
-  </si>
-  <si>
-    <t>DissolutionField</t>
-  </si>
-  <si>
-    <t>裂解力场</t>
-  </si>
-  <si>
-    <t>对所有敌人赋予裂解。获得等于敌人数量×3的格挡。升级：获得×5的格挡。</t>
-  </si>
-  <si>
     <t>SKI_UNC_10</t>
   </si>
   <si>
@@ -2163,9 +2139,6 @@
     <t>QuickIgnition</t>
   </si>
   <si>
-    <t>快速点燃</t>
-  </si>
-  <si>
     <t>选择手牌中一张牌，使其获得萤火属性。抽1张牌。升级：抽2张牌。</t>
   </si>
   <si>
@@ -2179,9 +2152,6 @@
   </si>
   <si>
     <t>生命因何而沉睡</t>
-  </si>
-  <si>
-    <t>生命值上限减少10点。本场战斗获得3点能量。升级：减少8点，获得4点能量。</t>
   </si>
   <si>
     <t>风险/能量</t>
@@ -2699,6 +2669,34 @@
   </si>
   <si>
     <t>何物朝向死亡</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤金之梦</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>终竟的明天</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>无梦的长夜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>萤火燎原</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>激发手牌中所有萤火牌。升级：费用0。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>打出手牌中所有的萤火牌。升级：费用0。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值上限减少1点。本场战斗每回合获得2点能量。升级：获得3点能量。</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -6730,7 +6728,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr defaultColWidth="7.796875" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.59765625" style="1" customWidth="1"/>
@@ -6788,7 +6786,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>423</v>
@@ -6806,7 +6804,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
       <c r="D3" s="5">
         <v>1</v>
@@ -6818,7 +6816,7 @@
         <v>426</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>427</v>
@@ -6842,10 +6840,10 @@
         <v>75</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>429</v>
@@ -6954,10 +6952,10 @@
         <v>26</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>441</v>
@@ -6981,7 +6979,7 @@
         <v>32</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>443</v>
@@ -7067,7 +7065,7 @@
         <v>455</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>456</v>
@@ -7121,7 +7119,7 @@
         <v>136</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>461</v>
@@ -7147,7 +7145,7 @@
         <v>19</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>463</v>
@@ -7203,7 +7201,7 @@
         <v>51</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>470</v>
@@ -7259,10 +7257,10 @@
         <v>104</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>476</v>
@@ -7286,10 +7284,10 @@
         <v>80</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>478</v>
@@ -7313,7 +7311,7 @@
         <v>55</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>480</v>
@@ -7369,10 +7367,10 @@
         <v>487</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>488</v>
@@ -7387,10 +7385,10 @@
         <v>21</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="D24" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>60</v>
@@ -7399,18 +7397,18 @@
         <v>61</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>490</v>
+        <v>851</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>432</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>21</v>
@@ -7419,7 +7417,7 @@
         <v>42</v>
       </c>
       <c r="D25" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>65</v>
@@ -7428,18 +7426,18 @@
         <v>66</v>
       </c>
       <c r="G25" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="I25" s="5" t="s">
         <v>493</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>21</v>
@@ -7454,13 +7452,13 @@
         <v>94</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>95</v>
@@ -7468,7 +7466,7 @@
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>41</v>
@@ -7480,22 +7478,22 @@
         <v>2</v>
       </c>
       <c r="E27" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>501</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>503</v>
       </c>
       <c r="I27" s="5"/>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>41</v>
@@ -7507,22 +7505,22 @@
         <v>2</v>
       </c>
       <c r="E28" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="H28" s="5" t="s">
         <v>506</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>508</v>
       </c>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>41</v>
@@ -7534,22 +7532,22 @@
         <v>1</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>510</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>840</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>512</v>
       </c>
       <c r="I29" s="5"/>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>41</v>
@@ -7561,22 +7559,22 @@
         <v>1</v>
       </c>
       <c r="E30" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="H30" s="5" t="s">
         <v>514</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>841</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>516</v>
       </c>
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>41</v>
@@ -7594,18 +7592,18 @@
         <v>40</v>
       </c>
       <c r="G31" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="I31" s="5" t="s">
         <v>518</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>41</v>
@@ -7623,10 +7621,10 @@
         <v>142</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>436</v>
@@ -7634,7 +7632,7 @@
     </row>
     <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>41</v>
@@ -7646,25 +7644,25 @@
         <v>3</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="G33" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="H33" s="5" t="s">
         <v>526</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>528</v>
       </c>
       <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>48</v>
@@ -7673,27 +7671,27 @@
         <v>1</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="H34" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="I34" s="5" t="s">
         <v>532</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>48</v>
@@ -7702,24 +7700,24 @@
         <v>1</v>
       </c>
       <c r="E35" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>536</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>538</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>435</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>12</v>
@@ -7734,21 +7732,21 @@
         <v>192</v>
       </c>
       <c r="F36" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="I36" s="5" t="s">
         <v>542</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>12</v>
@@ -7760,24 +7758,24 @@
         <v>1</v>
       </c>
       <c r="E37" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>844</v>
-      </c>
-      <c r="G37" s="5" t="s">
+      <c r="I37" s="5" t="s">
         <v>547</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>12</v>
@@ -7789,24 +7787,24 @@
         <v>0</v>
       </c>
       <c r="E38" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="I38" s="5" t="s">
         <v>552</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>843</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>12</v>
@@ -7818,24 +7816,24 @@
         <v>1</v>
       </c>
       <c r="E39" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="G39" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="H39" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="I39" s="5" t="s">
         <v>558</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>12</v>
@@ -7847,16 +7845,16 @@
         <v>2</v>
       </c>
       <c r="E40" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>562</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>564</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>436</v>
@@ -7864,7 +7862,7 @@
     </row>
     <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>12</v>
@@ -7876,24 +7874,24 @@
         <v>3</v>
       </c>
       <c r="E41" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="G41" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="H41" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="I41" s="5" t="s">
         <v>568</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>12</v>
@@ -7905,24 +7903,24 @@
         <v>1</v>
       </c>
       <c r="E42" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="G42" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="H42" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="I42" s="5" t="s">
         <v>574</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>12</v>
@@ -7934,24 +7932,24 @@
         <v>2</v>
       </c>
       <c r="E43" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="G43" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="H43" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="I43" s="5" t="s">
         <v>579</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>12</v>
@@ -7963,24 +7961,24 @@
         <v>1</v>
       </c>
       <c r="E44" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="H44" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>855</v>
-      </c>
-      <c r="G44" s="5" t="s">
+      <c r="I44" s="5" t="s">
         <v>584</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>12</v>
@@ -7992,16 +7990,16 @@
         <v>2</v>
       </c>
       <c r="E45" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="G45" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="H45" s="5" t="s">
         <v>589</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>591</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>436</v>
@@ -8009,7 +8007,7 @@
     </row>
     <row r="46" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>12</v>
@@ -8021,24 +8019,24 @@
         <v>0</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>427</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>12</v>
@@ -8050,24 +8048,24 @@
         <v>2</v>
       </c>
       <c r="E47" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="H47" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="I47" s="5" t="s">
         <v>598</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="I47" s="5" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>12</v>
@@ -8079,16 +8077,16 @@
         <v>1</v>
       </c>
       <c r="E48" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="G48" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="H48" s="5" t="s">
         <v>603</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>605</v>
       </c>
       <c r="I48" s="5" t="s">
         <v>436</v>
@@ -8096,7 +8094,7 @@
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="4" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>12</v>
@@ -8108,24 +8106,24 @@
         <v>2</v>
       </c>
       <c r="E49" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="G49" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="H49" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="I49" s="5" t="s">
         <v>609</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>12</v>
@@ -8137,24 +8135,24 @@
         <v>1</v>
       </c>
       <c r="E50" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="H50" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="I50" s="5" t="s">
         <v>614</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>846</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>12</v>
@@ -8166,24 +8164,24 @@
         <v>2</v>
       </c>
       <c r="E51" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="G51" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="H51" s="5" t="s">
         <v>619</v>
       </c>
-      <c r="G51" s="5" t="s">
+      <c r="I51" s="5" t="s">
         <v>620</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="I51" s="5" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>12</v>
@@ -8195,24 +8193,24 @@
         <v>3</v>
       </c>
       <c r="E52" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="H52" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="I52" s="5" t="s">
         <v>625</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>12</v>
@@ -8224,24 +8222,24 @@
         <v>1</v>
       </c>
       <c r="E53" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="I53" s="5" t="s">
         <v>629</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>856</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>851</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>12</v>
@@ -8253,24 +8251,24 @@
         <v>2</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>12</v>
@@ -8282,24 +8280,24 @@
         <v>0</v>
       </c>
       <c r="E55" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="I55" s="5" t="s">
         <v>636</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>849</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>847</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>21</v>
@@ -8311,24 +8309,24 @@
         <v>1</v>
       </c>
       <c r="E56" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="H56" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="F56" s="5" t="s">
-        <v>853</v>
-      </c>
-      <c r="G56" s="5" t="s">
+      <c r="I56" s="5" t="s">
         <v>641</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>21</v>
@@ -8340,24 +8338,24 @@
         <v>1</v>
       </c>
       <c r="E57" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="I57" s="5" t="s">
         <v>645</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>821</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>820</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="I57" s="5" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="4" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>21</v>
@@ -8369,24 +8367,24 @@
         <v>0</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>21</v>
@@ -8398,24 +8396,24 @@
         <v>1</v>
       </c>
       <c r="E59" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="G59" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="H59" s="5" t="s">
         <v>653</v>
       </c>
-      <c r="G59" s="5" t="s">
+      <c r="I59" s="5" t="s">
         <v>654</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="I59" s="5" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>21</v>
@@ -8427,24 +8425,24 @@
         <v>1</v>
       </c>
       <c r="E60" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="G60" s="5" t="s">
         <v>658</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="H60" s="5" t="s">
         <v>659</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="I60" s="5" t="s">
         <v>660</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="I60" s="5" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="4" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>21</v>
@@ -8456,24 +8454,24 @@
         <v>1</v>
       </c>
       <c r="E61" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="I61" s="5" t="s">
         <v>664</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>666</v>
-      </c>
-      <c r="I61" s="5" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="4" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>21</v>
@@ -8485,16 +8483,16 @@
         <v>2</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>436</v>
@@ -8502,7 +8500,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B63" t="s">
         <v>21</v>
@@ -8514,24 +8512,24 @@
         <v>1</v>
       </c>
       <c r="E63" t="s">
+        <v>669</v>
+      </c>
+      <c r="F63" t="s">
+        <v>848</v>
+      </c>
+      <c r="G63" t="s">
+        <v>670</v>
+      </c>
+      <c r="H63" t="s">
+        <v>671</v>
+      </c>
+      <c r="I63" t="s">
         <v>672</v>
-      </c>
-      <c r="F63" t="s">
-        <v>673</v>
-      </c>
-      <c r="G63" t="s">
-        <v>674</v>
-      </c>
-      <c r="H63" t="s">
-        <v>675</v>
-      </c>
-      <c r="I63" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B64" t="s">
         <v>21</v>
@@ -8540,27 +8538,27 @@
         <v>28</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="F64" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="G64" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="H64" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="I64" t="s">
-        <v>436</v>
+        <v>677</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B65" t="s">
         <v>21</v>
@@ -8569,27 +8567,27 @@
         <v>28</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="F65" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="G65" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="H65" t="s">
-        <v>508</v>
+        <v>644</v>
       </c>
       <c r="I65" t="s">
-        <v>685</v>
+        <v>648</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B66" t="s">
         <v>21</v>
@@ -8598,56 +8596,56 @@
         <v>28</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="F66" t="s">
-        <v>688</v>
+        <v>850</v>
       </c>
       <c r="G66" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="H66" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="I66" t="s">
-        <v>650</v>
+        <v>685</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B67" t="s">
         <v>21</v>
       </c>
       <c r="C67" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="F67" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="G67" t="s">
-        <v>693</v>
+        <v>853</v>
       </c>
       <c r="H67" t="s">
-        <v>675</v>
+        <v>689</v>
       </c>
       <c r="I67" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B68" t="s">
         <v>21</v>
@@ -8656,27 +8654,27 @@
         <v>42</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F68" t="s">
-        <v>697</v>
+        <v>849</v>
       </c>
       <c r="G68" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="H68" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="I68" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="B69" t="s">
         <v>21</v>
@@ -8685,27 +8683,27 @@
         <v>42</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="F69" t="s">
-        <v>676</v>
+        <v>698</v>
       </c>
       <c r="G69" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="H69" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="I69" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B70" t="s">
         <v>21</v>
@@ -8714,27 +8712,27 @@
         <v>42</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="F70" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G70" t="s">
-        <v>709</v>
+        <v>820</v>
       </c>
       <c r="H70" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="I70" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="B71" t="s">
         <v>21</v>
@@ -8743,56 +8741,56 @@
         <v>42</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="F71" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="G71" t="s">
-        <v>830</v>
+        <v>710</v>
       </c>
       <c r="H71" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="I71" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B72" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C72" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D72">
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="F72" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="G72" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="H72" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="I72" t="s">
-        <v>722</v>
+        <v>574</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="B73" t="s">
         <v>41</v>
@@ -8801,27 +8799,27 @@
         <v>28</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="F73" t="s">
-        <v>725</v>
+        <v>675</v>
       </c>
       <c r="G73" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="H73" t="s">
-        <v>727</v>
+        <v>506</v>
       </c>
       <c r="I73" t="s">
-        <v>576</v>
+        <v>721</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="B74" t="s">
         <v>41</v>
@@ -8830,27 +8828,27 @@
         <v>28</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="F74" t="s">
-        <v>683</v>
+        <v>724</v>
       </c>
       <c r="G74" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="H74" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="I74" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B75" t="s">
         <v>41</v>
@@ -8862,24 +8860,24 @@
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="F75" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="G75" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="H75" t="s">
-        <v>488</v>
+        <v>731</v>
       </c>
       <c r="I75" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B76" t="s">
         <v>41</v>
@@ -8888,27 +8886,27 @@
         <v>28</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="F76" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="G76" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="H76" t="s">
-        <v>741</v>
+        <v>557</v>
       </c>
       <c r="I76" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="B77" t="s">
         <v>41</v>
@@ -8917,27 +8915,27 @@
         <v>28</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="F77" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="G77" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="H77" t="s">
-        <v>559</v>
+        <v>603</v>
       </c>
       <c r="I77" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="B78" t="s">
         <v>41</v>
@@ -8946,27 +8944,27 @@
         <v>28</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="F78" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="G78" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="H78" t="s">
-        <v>605</v>
+        <v>506</v>
       </c>
       <c r="I78" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="B79" t="s">
         <v>41</v>
@@ -8975,27 +8973,27 @@
         <v>28</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="F79" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="G79" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="H79" t="s">
-        <v>508</v>
+        <v>694</v>
       </c>
       <c r="I79" t="s">
-        <v>757</v>
+        <v>695</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="B80" t="s">
         <v>41</v>
@@ -9004,56 +9002,56 @@
         <v>28</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="F80" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="G80" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="H80" t="s">
-        <v>704</v>
+        <v>756</v>
       </c>
       <c r="I80" t="s">
-        <v>705</v>
+        <v>436</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="B81" t="s">
         <v>41</v>
       </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D81">
         <v>2</v>
       </c>
       <c r="E81" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="F81" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="G81" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="H81" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="I81" t="s">
-        <v>436</v>
+        <v>762</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B82" t="s">
         <v>41</v>
@@ -9065,24 +9063,24 @@
         <v>2</v>
       </c>
       <c r="E82" t="s">
+        <v>764</v>
+      </c>
+      <c r="F82" t="s">
+        <v>765</v>
+      </c>
+      <c r="G82" t="s">
+        <v>766</v>
+      </c>
+      <c r="H82" t="s">
+        <v>767</v>
+      </c>
+      <c r="I82" t="s">
         <v>768</v>
-      </c>
-      <c r="F82" t="s">
-        <v>769</v>
-      </c>
-      <c r="G82" t="s">
-        <v>770</v>
-      </c>
-      <c r="H82" t="s">
-        <v>771</v>
-      </c>
-      <c r="I82" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B83" t="s">
         <v>41</v>
@@ -9091,27 +9089,27 @@
         <v>42</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" t="s">
-        <v>774</v>
+        <v>291</v>
       </c>
       <c r="F83" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="G83" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="H83" t="s">
-        <v>777</v>
+        <v>526</v>
       </c>
       <c r="I83" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="B84" t="s">
         <v>41</v>
@@ -9120,27 +9118,27 @@
         <v>42</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" t="s">
-        <v>291</v>
+        <v>774</v>
       </c>
       <c r="F84" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="G84" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="H84" t="s">
-        <v>528</v>
+        <v>777</v>
       </c>
       <c r="I84" t="s">
-        <v>782</v>
+        <v>436</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="B85" t="s">
         <v>41</v>
@@ -9149,27 +9147,27 @@
         <v>42</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="F85" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="G85" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="H85" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="I85" t="s">
-        <v>436</v>
+        <v>721</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B86" t="s">
         <v>41</v>
@@ -9178,27 +9176,27 @@
         <v>42</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="F86" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="G86" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="H86" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="I86" t="s">
-        <v>731</v>
+        <v>788</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B87" t="s">
         <v>41</v>
@@ -9207,51 +9205,22 @@
         <v>42</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="F87" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="G87" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="H87" t="s">
-        <v>797</v>
+        <v>557</v>
       </c>
       <c r="I87" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A88" t="s">
-        <v>799</v>
-      </c>
-      <c r="B88" t="s">
-        <v>41</v>
-      </c>
-      <c r="C88" t="s">
-        <v>42</v>
-      </c>
-      <c r="D88">
-        <v>1</v>
-      </c>
-      <c r="E88" t="s">
-        <v>800</v>
-      </c>
-      <c r="F88" t="s">
-        <v>801</v>
-      </c>
-      <c r="G88" t="s">
-        <v>802</v>
-      </c>
-      <c r="H88" t="s">
-        <v>559</v>
-      </c>
-      <c r="I88" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>
@@ -9272,42 +9241,42 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
     </row>
   </sheetData>
